--- a/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
+++ b/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
@@ -595,7 +595,6 @@
       <c r="P2" t="n">
         <v>2026</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
@@ -679,7 +678,6 @@
       <c r="P3" t="n">
         <v>2026</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
@@ -856,7 +854,6 @@
       <c r="P5" t="n">
         <v>2026</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
@@ -940,7 +937,6 @@
       <c r="P6" t="n">
         <v>2026</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
@@ -1024,7 +1020,6 @@
       <c r="P7" t="n">
         <v>2026</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
@@ -1108,7 +1103,6 @@
       <c r="P8" t="n">
         <v>2026</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
@@ -1192,7 +1186,6 @@
       <c r="P9" t="n">
         <v>2026</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
@@ -1276,7 +1269,6 @@
       <c r="P10" t="n">
         <v>2026</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
@@ -1360,7 +1352,6 @@
       <c r="P11" t="n">
         <v>2026</v>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
@@ -1444,7 +1435,6 @@
       <c r="P12" t="n">
         <v>2026</v>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
@@ -1528,7 +1518,6 @@
       <c r="P13" t="n">
         <v>2026</v>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
@@ -1612,7 +1601,6 @@
       <c r="P14" t="n">
         <v>2026</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
@@ -1696,7 +1684,6 @@
       <c r="P15" t="n">
         <v>2026</v>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
@@ -1871,7 +1858,6 @@
       <c r="P17" t="n">
         <v>2026</v>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
@@ -1955,7 +1941,6 @@
       <c r="P18" t="n">
         <v>2026</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
@@ -2039,7 +2024,6 @@
       <c r="P19" t="n">
         <v>2025</v>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
@@ -2123,7 +2107,6 @@
       <c r="P20" t="n">
         <v>2025</v>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
@@ -2207,7 +2190,6 @@
       <c r="P21" t="n">
         <v>2025</v>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
@@ -2291,7 +2273,6 @@
       <c r="P22" t="n">
         <v>2025</v>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
@@ -2375,7 +2356,6 @@
       <c r="P23" t="n">
         <v>2025</v>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>Summons Voided / Officer Discipline</t>
@@ -2459,7 +2439,6 @@
       <c r="P24" t="n">
         <v>2025</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>Resigned &amp; Criminally Charged</t>
@@ -2543,7 +2522,6 @@
       <c r="P25" t="n">
         <v>2025</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
@@ -2627,7 +2605,6 @@
       <c r="P26" t="n">
         <v>2025</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
@@ -2711,7 +2688,6 @@
       <c r="P27" t="n">
         <v>2025</v>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
@@ -2886,7 +2862,6 @@
       <c r="P29" t="n">
         <v>2024</v>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
@@ -3078,7 +3053,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FLK-2024-030</t>
+          <t>ALPR-2024-030</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -3152,7 +3127,6 @@
       <c r="P32" t="n">
         <v>2024</v>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>Relieved of Duty / Under Investigation</t>
@@ -3236,7 +3210,6 @@
       <c r="P33" t="n">
         <v>2024</v>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
@@ -3502,7 +3475,6 @@
       <c r="P36" t="n">
         <v>2023</v>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
@@ -3677,7 +3649,6 @@
       <c r="P38" t="n">
         <v>2021</v>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
@@ -3761,7 +3732,6 @@
       <c r="P39" t="n">
         <v>2020</v>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
@@ -3845,7 +3815,6 @@
       <c r="P40" t="n">
         <v>2020</v>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>

--- a/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
+++ b/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Verified_Incidents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KPI_Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Verified Incidents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,17 +27,28 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0392B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF6F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,13 +56,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,8 +450,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="48" customWidth="1" min="18" max="18"/>
+    <col width="47" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -519,3473 +572,4196 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-001</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Pasadena Police Department</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Sgt. Michael Palitz</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Co-worker Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Repeated ('Overwhelming Use' Flagged by System)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>An active internal investigation revealed Sgt. Palitz allegedly abused the Pasadena Police Department's Flock Safety license plate reader camera system to track and stalk a female fellow police officer. According to City Council Member Emmanuel Guerrero, the abuse involved such 'overwhelming use' that the automated system itself flagged the account and notified department administrators. Palitz resigned while under active investigation.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Automated system flag / internal notification triggered by overwhelming volume of searches</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Resigned from the police department in July 2026 while under active internal investigation; investigation remains ongoing.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>KPRC 2 Click2Houston Investigative Report (July 10, 2026)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>https://www.click2houston.com/news/local/2026/07/10/pasadena-police-sergeant-resigns-while-under-internal-investigation-council-member-cites-alleged-misuse-of-flock-camer/</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>KPRC 2 Click2Houston Jul 10 2026: Palitz resigned under investigation; Councilmember Guerrero alleges Flock co-worker stalking; Dept confirms investigation continues.</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-002</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Albany Police Department</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Tytianna Davis, Jade Jackson, Nicholas Richardson, Brittney Smith, Issac Whitus (5 Officers)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Repeated (Unspecified)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>An internal agency audit revealed that five officers repeatedly accessed the city's Flock Safety LPR camera system for personal, non-law enforcement purposes. The officers used automated plate tracking data to monitor individuals without legitimate investigative justification.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Internal department audit of Flock ALPR search logs; requested GBI investigation</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>All five officers were terminated immediately and arrested by the Georgia Bureau of Investigation (GBI); charged with felony violation of oath of office and misuse of license plate data.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Georgia Bureau of Investigation (GBI) Official Press Release (July 2026)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>https://gbi.georgia.gov/press-releases/2026-07-06/gbi-arrests-five-former-albany-police-department-officers-misuse-license</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>GBI Jul 6 2026 press release confirms five former Albany officers arrested for Misuse of License Plate Data + Violation of Oath after Flock audit.</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-003</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Milwaukee Police Department</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Detective Tehrangi Chapman (Internal Affairs)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking / GPS Tracking</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>An Internal Affairs detective assigned to investigate another officer's ALPR stalking case used MPD's Flock camera network 20 times between Jan 2024 and Jan 2025 to stalk two individuals. He logged queries under false justifications like 'training' and 'test', and secretly installed an unauthorized GPS tracking device on one victim's vehicle.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Victim report to police regarding stalking and discovery of physical GPS device</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Suspended with pay; charged by Milwaukee County DA in July 2026 with felony misconduct in public office and misdemeanor GPS device misuse.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Urban Milwaukee / Milwaukee County criminal complaint (Jul 2026)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>https://urbanmilwaukee.com/2026/07/09/mpd-investigator-in-flock-stalking-case-now-accused-of-own-misuse/</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Urban Milwaukee / FOX6 / TMJ4 Jul 2026: IA Det. Tehrangi Chapman charged with felony misconduct + GPS-device misuse after Flock audit during Ayala investigation; 20 searches logged as training/test.</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2024-2025</t>
         </is>
       </c>
-      <c r="Q4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>ALPR/GPS misuse documented Jan 2024–Jan 2025; felony misconduct charges filed July 2026. Canonical Year=2026 matches Case_ID / charging year.</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-004</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Cherokee County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Lt. Chris Bryant, Sgt. Mike Creeden, Deputy Cynthia Jodesty</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>A self-initiated audit by the agency's Real-Time Intelligence Division uncovered anomalies in Flock search logs involving two supervisors and one deputy. Investigation confirmed all three used LPR cameras to track license plates for personal reasons unrelated to official police duties.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Internal audit by Real-Time Intelligence Division</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>All three deputies were fired and arrested; charged with felony violation of oath of office and misdemeanor unlawful retention of license plate reader data.</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / CBS News Atlanta (June 2026)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/2-more-cherokee-deputies-accused-of-misusing-license-plate-reader-database/</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>AJC Jun 2026: Cherokee deputies Cynthia Jodesty, Lt Chris Bryant, Sgt Mike Creeden fired+charged for non-LE LPR database misuse after audit.</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-005</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Richmond County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Sheriff's Deputy (Unnamed in state report)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Personal Tracking / Unauthorized Search</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>A Richmond County deputy was arrested and charged after an audit revealed they had used the department's automated license plate recognition database for non-law enforcement personal tracking.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Internal department database audit</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Arrested and criminally charged; employment terminated.</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution Statewide ALPR Audit Report (June 2026)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-006</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Greene County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Deputy Quinsha Goss</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Personal Tracking / Stalking</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Multiple (Over 3 Months)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>A departmental audit found that Deputy Goss accessed Flock license plate readers to run searches involving at least one license plate for personal reasons over a 3-month period without any law enforcement mandate.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Internal audit of Flock camera search logs</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Terminated from employment; arrested and charged with violation of oath of office and misuse of LPR data.</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>CBS News Atlanta / Greene County Sheriff's Office (June 2026)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/07/more-georgia-officers-arrested-for-flock-camera-misuse-officials-say/</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>AJC Jul 2026: Greene County Dep. Quinsha Goss arrested after Flock audit found unauthorized plate queries.</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-007</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Menasha Police Department</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Officer Cristian Morales</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Officer Morales utilized the city's Flock ALPR camera network to track an ex-girlfriend, running multiple unauthorized searches without legitimate investigative justification.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Internal department audit and victim reporting</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Placed on administrative leave; criminally charged with felony misconduct in public office in Feb 2026.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>The Marshall Project / Wisconsin Freedom of Information Council</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Marshall Project / IJ: Menasha Officer Cristian Morales; ex-girlfriend complaint; charged misconduct; administrative leave.</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-008</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Bonner Springs Police Department</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Detective Kyle Rector</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Detective Rector allegedly used automated license plate readers to track his estranged wife and two men he suspected were her new romantic partners without law enforcement authorization.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Internal affairs audit and victim complaint</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Criminally charged with multiple stalking and computer crime offenses in March 2026.</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>KCUR Radio / Institute for Justice Review</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>KBI/KCTV/KSHB: Kyle Rector fired Jan 26 2026; charged Mar 2026 incl. Flock/LPR stalking of estranged wife + other offenses.</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-009</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>San Francisco Police Department</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>SFPD Patrol Officer (Unnamed in report)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Conflict of Interest / Unauthorized Search</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>An officer used SFPD's Flock ALPR system to locate his wife's stolen car for personal reasons, violating department rules regarding conflicts of interest. He then posted an image of the vehicle on social media.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>An officer in a neighboring jurisdiction recognized the unauthorized social media post</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Subjected to formal internal affairs investigation for violating police surveillance protocols in March 2026.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>The San Francisco Standard / The Marshall Project</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>Marshall Project: SFPD officer investigated for ALPR search re: wife stolen car / conflict of interest.</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-010</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>MO</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Joplin Police Department</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Patrol Officer (Unnamed in agency disclosure)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Excessive Tracking</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>395</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>An officer was discovered to have abused the department's Flock Safety database by conducting 395 unauthorized searches on a single license plate without any active investigative case.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Investigation and records analysis by local transparency group DeFlock Joplin</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>Officer was formally terminated from the police department in January 2026.</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>KCUR Kansas City / DeFlock Joplin Investigation</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-011</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Monroe County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Sheriff's Deputy Lamar Roman</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Stalking / Unlawful Traffic Stop</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Deputy Roman allegedly used an ALPR system to track and eventually pull over a woman he had met while providing off-duty security on a television set, monitoring her private vehicular movements.</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Victim complaint and internal affairs investigation</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Arrested in 2026 and charged with accessing a computer or electronic device without authorization.</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Monroe County SO / Local 10 / Law&amp;Crime (Mar 2026)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>https://www.local10.com/news/local/2026/03/10/florida-keys-deputy-arrested-on-computer-crimes-charges/</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Local10 / Law&amp;Crime / 404 Media: Dep. Lamar Eliseo Roman fired+arrested Mar 2026; DAVID/ALPR hotlist + unauthorized stop of woman met on Bad Monkey set. Primary Monroe County case. Canonical Monroe County Lamar Roman record (FLK-2024-031 removed as duplicate of this case).</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-012</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Prairie Grove &amp; Holiday Hills Police Dept.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Officer / Chief William C. Copp</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Officer Copp, who simultaneously served as Police Chief of nearby Holiday Hills, abused authorized police access to search Flock ALPR databases for vehicle locations of several former romantic partners and at least one of their new partners.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Internal police investigation and victim reporting</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Arrested in 2026 and criminally charged with official misconduct and LPR misuse.</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>IJ Plate Privacy list: Officer/Chief William C. Copp Prairie Grove/Holiday Hills; arrested for Flock searches of former romantic partners.</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-013</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>San Francisco PD &amp; Los Altos PD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Municipal Operators &amp; Federal Agencies</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Mass Surveillance / Illegal Data Sharing</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,600,000+ (Systemic)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>A class action lawsuit revealed that federal immigration and law enforcement agencies accessed SFPD's Flock cameras over 1.6 million times, while Los Altos shared data over 1 million times with out-of-state agencies, violating California statutory privacy laws designed to protect civil liberties and immigrant communities.</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Public records disclosures and class action legal investigation</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Class action lawsuit filed by Gibbs Mura against Flock Safety and municipal operators seeking statutory damages ($2,500/violation) and injunctions.</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Gibbs Mura Class Action Complaint / California Civil Code § 1798.90.54 (April 2026)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>https://www.classlawgroup.com/flock-safety-license-plate-reader-cameras-lawsuit</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-014</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>San Diego Police Department</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Detective Gary Gonzales / Patrol Officers</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / False Arrest</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>San Diego police relied on a false Flock hit to arrest Ariel Beltran and Parra at gunpoint inside a cigar lounge for an attempted carjacking 5 miles away. The camera hit occurred before the pursuit began, proving physical impossibility, yet police ignored cell phone location alibis and arrested both men.</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Defense investigation proving physical alibi and impossible timestamp synchronization</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>Criminal charges dismissed; victims filed formal civil rights tort claims seeking $1.5 million apiece in damages in April 2026.</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Times of San Diego Legal Investigation (June 2026)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>https://timesofsandiego.com/crime/2026/06/07/a-flock-license-plate-reader-linked-a-san-diego-man-to-a-violent-crime-he-was-five-miles-away/</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Times of San Diego Jun 2026: Hugo Parra AI vehicle match false positive; jailed ~1 month; charges dropped.</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-015</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>MN</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Plymouth Police Department</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / False Stop</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Multi-day Flock tracking; high-risk box-and-pin stop June 28, 2026</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Automotive journalist Joel Feder and his wife were boxed in by four Plymouth PD squad cars outside a Kohl's after Flock ALPR alerts on a Range Rover press loaner. Police had tracked the vehicle for days via Flock. Root cause: a lost NJ manufacturer plate reported in California was entered into NCIC incomplete as 34 DTM (missing small middle digits); Feder's plate was 34 10 DTM, and Flock OCR also missed those characters. VIN clean; original plate was lost, not stolen; ~1 hour detention.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Roadside verification (VIN/plate); Plymouth PD statement; Feder first-person account; local TV body-cam reporting</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Released at scene without charges; Plymouth PD attributed alerts to incomplete NCIC entry; Flock stated it was reviewing the incident.</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>The Drive (Feder) / FOX 9 Minneapolis / CBS Minnesota</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>https://www.thedrive.com/news/how-flock-cameras-wrongly-tracked-me-for-days-over-stolen-plates-and-sent-police-after-me</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Primary: Feder The Drive first-person. Local TV: FOX 9 (https://www.fox9.com/news/minnesota-car-reviewer-flock-camera) and CBS Minnesota/WCCO (https://www.cbsnews.com/minnesota/news/flock-cameras-wrongly-flag-plates-as-stolen/). Cross-listed as AI Wrongful Enforcement Database ID 42.</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Incident late June 2026 (NCIC entry June 24; Flock alerts June 26 and June 28 stop).</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Released / No Charges — Documented False Stop</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-016</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Cherry Hills Village Police Dept.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Wrongful Stop</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Flock Safety camera data led police to conduct an improper traffic stop on an innocent driver due to character misinterpretation and database synchronization errors.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Roadside investigation and license plate verification</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Driver released without charges; documented in national civil rights review of ALPR accuracy failures.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S17" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-017</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sherwood Police Department</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Gunpoint Detention</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>A Flock camera misread the license plate of an SUV, leading officers to detain an innocent couple at gunpoint while their six-week-old baby sat alone in a car seat in the back of the vehicle.</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Roadside verification after armed detention</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Officers admitted the AI camera error on scene ('I'm not gonna say they're completely perfect...'); documented in national civil rights review.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-018</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Milwaukee Police Department</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Officer Josue Ayala</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Officer Ayala conducted 179 unauthorized searches in the Flock Safety system using a single-word justification ('investigation') to stalk a dating partner (&gt;50 searches) and their ex-partner (&gt;100 searches).</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Victim self-searched license plate on haveibeenflocked.com and reported unauthorized police hits to MPD</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>Charged with attempted misconduct in public office; pleaded guilty; resigned from MPD.</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>The Marshall Project / Novara Media Investigation</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>Marshall Project / Urban Milwaukee / IJ: Ayala ~179 Flock searches of dating partner + ex; charged; pleaded; resigned.</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S19" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-019</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Braselton Police Department</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Police Chief Michael Steffman</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Police Chief Steffman abused municipal license plate reader databases to actively track, stalk, and harass multiple people, including a former romantic partner.</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Georgia Bureau of Investigation (GBI) criminal probe</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Resigned as Police Chief in Nov 2025; arrested by GBI on criminal stalking and misconduct charges.</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / GBI Report (Nov 2025)</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>AJC/GBI: Braselton Chief Michael Steffman; ALPR misuse + stalking/harassment; resigned then arrested.</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-020</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Coffee County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Former Deputy Chris Rozar</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Deputy Rozar utilized the department's Flock Safety ALPR database to monitor the movements of a woman he was romantically interested in, tracking her vehicle locations without her consent or any active criminal case.</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Victim complaint and subsequent internal investigation</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>Fired from the department at the onset of the investigation; criminally charged with multiple offenses.</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / Institute for Justice</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>IJ/AJC: Coffee County former Dep. Chris Rozar charged after Flock stalking of romantic interest; fired.</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S21" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-021</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Echols County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Anna Altobello (Civilian Secretary)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Personal Tracking / Stalking</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Multiple (8 Felony Counts)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>A civilian secretary at the sheriff's office accessed the agency's Flock Safety account on multiple occasions for non-law enforcement purposes, conducting unauthorized tag searches on two acquaintances.</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Sheriff requested GBI investigation following an external tip</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Arrested by GBI; charged with 8 counts of Misuse of License Plate Data, Stalking, Family Violence Stalking, and Violation of Oath of Office.</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / GBI Investigation</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S22" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-022</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Columbine Valley Police Department</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Sgt. Jamie Milliman</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Wrongful Accusation / Flawed AI Evidence</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Sgt. Milliman relied blindly on a Flock ALPR camera hit to accuse Denver resident Chrisanna Elser of stealing a $25 package. Police issued a criminal summons without verifying obvious discrepancies. Elser had to obtain her own vehicle's onboard Rivian video to prove she was miles away when the theft occurred.</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Victim presented video alibi proving the Flock hit and police accusation completely false</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>Criminal summons voided after Elser provided exculpatory GPS/video evidence; formal disciplinary action / training ordered for Sgt. Milliman per reporting.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>The Colorado Sun / 404 Media Investigation</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>https://coloradosun.com/2025/10/28/flock-camera-police-colorado-columbine-valley/</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>Colorado Sun Oct 28 2025 (and Nov discipline follow-ups): Sgt Milliman / Chrisanna Elser wrongful package-theft summons via Flock; summons voided; reprimand + training.</t>
         </is>
       </c>
-      <c r="P23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr">
         <is>
           <t>Summons Voided / Officer Discipline</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-023</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>KY</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Louisville Metro Police Department</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Officer Roberto Cedeno</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Hundreds</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Officer Cedeno utilized the city's automated license plate reader system to track an ex-partner and her friends hundreds of times over a two-month period without any legitimate law enforcement objective.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Internal affairs audit and victim reporting</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Resigned April 2025 before termination proceedings finished; indicted on multiple felony charges including stalking and unlawful computer access (Courier Journal / LMPD).</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice Nationwide ALPR Review</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>IJ: Louisville Officer Roberto Cedeno charged after ALPR tracking of ex + friends hundreds of times.</t>
         </is>
       </c>
-      <c r="P24" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S24" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-024</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>King County Sheriff's Office / Covington</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Deputy Welch</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Excessive Force</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Deputy Welch received a false Flock Safety alert for a stolen van, drove to a gas station, and tackled an innocent man to the ground, grabbing his waist and forcing him face-down onto pavement in a violent wrongful detention.</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>King County Office of Law Enforcement Oversight (OLEO) independent investigation</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>Formal oversight investigation confirming lack of probable cause and reliance on unverified Flock alert.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>King County OLEO Investigation Report #2025-006</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>https://cdn.kingcounty.gov/-/media/king-county/independent/governance-and-leadership/government-oversight/office-of-law-enforcement-oversight/investigation-findings-memos/2026/oleo2025-006-fir.pdf</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S25" t="inlineStr">
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-025</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>City of El Cajon</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>City Police Department / Municipal Leadership</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Illegal Data Sharing / Mass Surveillance</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Systemic (Continuous)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>The City of El Cajon systematically violated California law by sharing Flock ALPR data feeds with out-of-state police agencies and federal border/immigration authorities without required legal guardrails or statutory oversight.</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Investigation by California Office of the Attorney General</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>California Attorney General Rob Bonta filed a formal lawsuit against the City of El Cajon in Oct 2025 to halt illegal ALPR data sharing.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>California Attorney General Lawsuit / CalECPA (Oct 2025)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>https://www.classlawgroup.com/flock-safety-license-plate-reader-cameras-lawsuit</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S26" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-026</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Buford City Schools Police Department</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>School Police Officers</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Mission Creep / Low-Level Surveillance</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>375+</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Between Jan 2025 and March 2026, school police ran more than 375 searches in ALPR tracking databases for low-level 'school residency verification' (RV), representing severe surveillance mission creep without criminal predicate.</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Electronic Frontier Foundation (EFF) nationwide audit log analysis</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>Exposed nationally by EFF as an unchecked administrative shortcut around legal due process.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>Electronic Frontier Foundation (EFF) Deep Links Investigation</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>https://www.eff.org/deeplinks/2026/05/more-license-plate-reader-mission-creep-school-residency-verification-background</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S27" t="inlineStr">
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-027</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Oak Ridge Police Department</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Officer Zachary D. Gauthier</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>18 (Flock-specific counts of 23 total)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Former Oak Ridge PD Officer Zachary Gauthier accessed the Flock ALPR system 18 times for personal (non-law-enforcement) use between February 25 and March 25, 2025, and also misused Accurint, the State Link System, and his patrol-car computer. An Anderson County Grand Jury indicted him on 23 counts of official misconduct (Class E felony) on July 1, 2025—18 counts specifically for Flock misuse. He was placed on leave April 21, 2025, fired April 24, 2025, and pleaded guilty to all 23 counts on March 23, 2026 (48 hours custody, supervised probation, POST surrender, judicial diversion eligibility). Oak Ridge shares Flock data within the same East Tennessee network as Maryville.</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Internal Oak Ridge PD complaints referred to Anderson County District Attorney General Dave Clark for independent investigation</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Terminated April 24, 2025; indicted July 1, 2025 on 23 counts of official misconduct; pleaded guilty March 23, 2026; sentenced March 2026 to two years on each count with 48 hours to serve, remainder suspended probation, judicial diversion eligibility (3B Media / WATE).</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>WBIR 10News / WATE 6 News / WVLT / Maryville Residents for Privacy / Anderson County DA</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>https://www.wbir.com/article/news/crime/da-former-oak-ridge-officer-pleads-guilty-23-counts-of-misconduct/51-c7b250d6-0843-4407-a0e2-2ecc68c2809a</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Documented on maryvilleprivacy.org (East TN regional Flock network context). Corroborated by WBIR indictment/plea coverage, WATE indictment detail (18 Flock counts), WVLT plea reporting (Mar 23, 2026), and Anderson County Grand Jury / DA Clark statements.</t>
         </is>
       </c>
-      <c r="P28" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>Year/Case_ID keyed to 2025 indictment/public charging; Incident_Year is Feb–Mar 2025 Flock queries; Resolution_Year is Mar 2026 guilty plea.</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>FLK-2024-027</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Matteson Police Department</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Officer Jaila Cole-Clark</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Hundreds</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Officer Cole-Clark conducted hundreds of unauthorized searches in the department's Flock Safety database to monitor the daily driving routes of her former domestic partner and that person's new partner.</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Internal investigation triggered by complaint; documents obtained via FOIA by stopflock.org</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>Officer resigned from the police department during the middle of the internal affairs investigation.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice Review / stopflock.org FOIA</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr">
         <is>
           <t>IJ/stopflock.org: Matteson Officer Jaila Cole-Clark; hundreds of Flock searches of former domestic partner; resigned mid-investigation.</t>
         </is>
       </c>
-      <c r="P29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="S29" t="inlineStr">
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>FLK-2024-028</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Orange City Police Department</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Officer Jarmarus Brown</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>100+</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Officer Brown allegedly used automated license plate readers to stalk his girlfriend and her family members more than 100 times over a seven-month span without any investigative basis.</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Internal audit and victim complaint</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Arrested and criminally charged in 2025; terminated from the police department.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>IJ: Orange City Officer Jarmarus Brown; 100+ ALPR hits on girlfriend/family; arrested 2025.</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Misuse window associated with 2024; arrested and criminally charged in 2025.</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>FLK-2024-029</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Riverside County Sheriff's Department</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Deputy Alexander Vanny</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Stalking / Kidnapping Facilitation</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>After being arrested for kidnapping his ex-fiancée, forensic audits revealed Deputy Vanny had used the department's ALPR system to illegally track one of her close friends to monitor their movements and gather intelligence.</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Criminal investigation into domestic kidnapping and stalking</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>Convicted by jury in Dec 2025 on multiple felony charges; terminated from Sheriff's Department.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice / Riverside County DA</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr">
         <is>
           <t>IJ: Riverside Dep. Alexander Vanny; Flock tracking of ex-fiancée friend after kidnapping arrest; convicted Dec 2025.</t>
         </is>
       </c>
-      <c r="P31" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>Underlying conduct associated with 2024; jury conviction Dec 2025.</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S31" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>ALPR-2024-030</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Shelby County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Deputy Thadius Gordon</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>ALPR (county database; Flock not confirmed in primary local coverage)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>100+</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Deputy Gordon accessed county ALPR tracking databases more than 100 times to stalk his ex-wife and monitor her vehicular movements across the jurisdiction without law enforcement purpose.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Victim complaint and internal audit</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Relieved of duty by Sheriff's Office; subjected to internal and criminal investigation.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice Nationwide ALPR Stalking Report</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>IJ + local reporting: Shelby County Dep. Thadius Gordon; 100+ ALPR tracks of ex-wife; relieved of duty. Primary local coverage describes SCSO plate databases — do not assert Flock without a primary vendor source.</t>
         </is>
       </c>
-      <c r="P32" t="n">
-        <v>2024</v>
-      </c>
-      <c r="S32" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>Relieved of Duty / Under Investigation</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>FLK-2024-032</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>York County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Wrongful Stop</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>An automated Flock camera misread alphanumeric characters on a passing license plate, generating an erroneous stolen vehicle alert that resulted in an improper traffic stop of an innocent driver.</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>Roadside verification of vehicle registration and VIN</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>Driver released; documented in Institute for Justice database of automated license plate reader errors.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P33" t="n">
-        <v>2024</v>
-      </c>
-      <c r="S33" t="inlineStr">
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>FLK-2024-033</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Niceville Police Department</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Former Officer Coty Hall</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Co-worker Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Officer Hall utilized the department's Flock camera network to unlawfully track the personal driving routes and movements of a fellow police officer and that officer's spouse.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Internal department audit and complaint</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Pleaded no contest to criminal charges; fired from the police department following arrest.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice / Florida Court Records</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>IJ: Niceville Officer Coty Hall; Flock tracking of coworker+spouse; pleaded no contest; fired (arrest ~Oct 2025).</t>
         </is>
       </c>
-      <c r="P34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Misuse discovery/ID year 2024; arrest ~Oct 2025 then plea / termination.</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>FLK-2023-034</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Costa Mesa Police Department</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Officer Robert Josett</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Multiple (Extended Period)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>Officer Josett utilized a Flock camera system to track the movements of his mistress as well as her other romantic interests over an extended period without law enforcement authorization.</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Internal affairs audit and complaint</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>Pleaded guilty to multiple criminal charges in April 2026; employment terminated.</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice / California Court Records</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t>IJ: Costa Mesa Officer Robert Josett; Flock track of mistress; pleaded guilty Apr 2026.</t>
         </is>
       </c>
-      <c r="P35" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>Misuse year 2023; pleaded guilty April 2026.</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>FLK-2023-035</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sedgwick Police Department</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Police Chief Lee Nygaard</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking / Physical Stalking</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Police Chief Nygaard used Flock cameras to track his ex-girlfriend's vehicles 228 times over four months and followed her and her new boyfriend in his police cruiser using real-time location alerts.</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Internal investigation and county reporting</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Resigned as Police Chief under investigation; documented by ACLU and Institute for Justice.</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>ACLU of Wisconsin / KCUR Report</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>https://www.aclu-wi.org/news/what-the-flock-police-surveillance-is-ripe-for-abuse/</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>IJ/ACLU-WI: Sedgwick Chief Lee Nygaard; 200+ Flock hits on ex + boyfriend; resigned.</t>
         </is>
       </c>
-      <c r="P36" t="n">
-        <v>2023</v>
-      </c>
-      <c r="S36" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>FLK-2022-036</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Kechi Police Department</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Lt. Victor Heiar</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>Lt. Heiar abused municipal Flock license plate tracking databases to monitor the movements of his estranged wife without her consent or any criminal investigation.</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>Victim complaint and internal audit</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>Pleaded guilty to criminal computer crime and stalking charges; terminated from police employment.</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>KCUR Radio / Kansas Court Records</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="3" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="3" t="inlineStr">
         <is>
           <t>IJ: Kechi Lt Victor Heiar; Flock track of estranged wife; pleaded guilty (IJ lists 2023 resolution year).</t>
         </is>
       </c>
-      <c r="P37" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2023</v>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>Misuse associated with 2022 cataloguing; IJ lists 2023 plea/resolution year.</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S37" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>FLK-2021-037</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Westmoreland County</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Officer Michael McSherry</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>ALPR / Automated Systems</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Repeated (Unspecified)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Officer McSherry repeatedly accessed automated license plate reader networks to track the vehicular movements of his estranged wife and several other family members.</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Internal police audit and criminal investigation</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Pleaded guilty to criminal stalking charges; stripped of police powers and employment.</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>IJ: Westmoreland Officer Michael McSherry; pleaded guilty to stalking via plate readers of estranged wife/family.</t>
         </is>
       </c>
-      <c r="P38" t="n">
-        <v>2021</v>
-      </c>
-      <c r="S38" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>FLK-2020-038</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Lenexa Police Department</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Police Department Leadership / Patrol Officers</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Retaliation / Political Targeting</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>After citizen Canyen Ashworth published a newspaper op-ed critical of local police cooperation with ICE, police retaliated by linking him to anti-ICE posters put up with glue around town. The Police Chief issued a 'MYOC' (Make Your Own Case) BOLO and utilized ALPR cameras to actively track his vehicle around town to manufacture a reason for a traffic stop.</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>Open records request by KCUR radio and legal intervention by ACLU of Kansas</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>Exposed nationally by ACLU as unconstitutional First Amendment retaliation and mass-surveillance abuse.</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>ACLU of Kansas / KCUR Radio Report</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="3" t="inlineStr">
         <is>
           <t>https://www.aclu.org/news/privacy-technology/tracking-alpr-cameras/alpr-against-op-ed-writer</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P39" t="n">
-        <v>2020</v>
-      </c>
-      <c r="S39" t="inlineStr">
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>FLK-2020-039</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Aurora Police Department</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>ALPR (In-car / Automated Reader)</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Gunpoint Detention</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>An ALPR system erroneously flagged Brittney Gilliam's minivan as a stolen vehicle (matching the plate number of a stolen motorcycle from Montana). Officers conducted a high-risk gunpoint stop, forcing four children (ages 6 to 17) to lie face-down in handcuffs on hot pavement before verifying the obvious vehicle mismatch.</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Viral bystander video by Jennifer Wurtz and internal police review</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>City paid $1.9 million settlement to the family; police issued formal apology; state legislature reformed high-risk traffic stop protocols.</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>AP News / CBS News Colorado / Institute for Justice</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>https://apnews.com/article/handcuffed-black-girls-colorado-settlement-a7a695839b8841e56b7db0d103cc5ed1</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Verified $1.9M Aurora settlement (AP Feb 2024); ALPR plate/state mismatch stop.</t>
         </is>
       </c>
-      <c r="P40" t="n">
-        <v>2020</v>
-      </c>
-      <c r="S40" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>FLK-2026-018</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Baytown Police Department</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Unnamed officer (not publicly identified)</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Unauthorized Access / Personal Tracking</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Allegations under investigation (count not public)</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>In late July 2026, Baytown Police Chief John Stringer announced allegations that one officer misused the city’s Flock Safety license plate reader system. Stringer authorized an internal affairs investigation and a separate criminal investigation, and asked the Harris County District Attorney’s Office to assist on the criminal probe. The officer has not been publicly named; allegations, not a finding of guilt.</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Agency receipt of allegations; chief public announcement; DA referral</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Internal affairs and criminal investigations opened (July 2026); Harris County DA assisting; no public disposition as of late July reporting.</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>KPRC 2 / Click2Houston; ABC13; Houston Chronicle</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.click2houston.com/news/local/2026/07/27/baytown-police-investigating-officer-accused-of-misusing-flock-license-plate-reader-system/</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>Chief Stringer public statement and DA referral confirmed in KPRC 2 / ABC13 / Chronicle late July 2026 coverage. Officer unnamed.</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>Announced late July 2026; probes ongoing.</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>Under Investigation / Pending</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TOTAL_UNIQUE_CASES</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>39</v>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>FLK-2026-019</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Greer Police Department</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Kareem Lynch; Sebastian Echeverry</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Romantic Stalking</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Repeated unauthorized searches (per separation documents summarized in reporting)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Greer Police terminated Kareem Lynch (June 26, 2026) and Sebastian Echeverry (June 29, 2026) after an internal investigation alleged unauthorized Flock searches. Reporting on separation documents says Lynch searched plates of an officer he had previously been in a relationship with and entered inaccurate reasons; Echeverry allegedly searched multiple plates and falsely entered “Alcohol Offense Non-DUI.” Department said no criminal charges. Allegations from IA, not court findings.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Internal investigation; separation documents described in Greenville Online reporting</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Both officers terminated (June 2026); no criminal charges announced per department.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Greenville Online (July 24, 2026)</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greenvilleonline.com/story/news/crime/2026/07/24/greer-pd-flock-scandal-upstate-police-oversight/90994284007/</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Greenville Online Jul 24 2026 names Lynch and Echeverry terminations and alleged false search reasons.</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Terminations late June 2026; public reporting July 24.</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Terminated / Resigned (Employment Fallout)</t>
+        </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STATES_REPRESENTED</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>16</v>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>FLK-2026-020</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sumter County Sheriff’s Office</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Detective Brandy Almany</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Romantic Stalking</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Multiple restricted-database lookups alleged (Flock + DAVID + CCIS)</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Sumter County Sheriff’s Office announced an internal audit flagged Det. Brandy Almany’s use of restricted databases. Agency alleges she used Flock ALPR, Florida’s DAVID, and CCIS to obtain information about her husband’s ex-wife for personal reasons, and used unrelated case numbers / false electronic records to make searches appear investigative. Arrested on official misconduct and computer-related charges and terminated. Sheriff Patrick Breeden ordered a complete internal audit and suspended the agency’s use of Flock pending review. Allegations, not a finding of guilt.</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Internal audit of restricted databases; sheriff public statement</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Arrested and terminated (July 2026); agency suspended Flock use during audit; charges pending.</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>WESH 2; WFTV 9; ClickOrlando / News 6</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wesh.com/article/sumter-detective-arrested-database-misuse/73251430</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>WESH/WFTV/ClickOrlando Jul 23–24 2026: arrest, termination, Flock suspension. Allegations pending.</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>Arrest/termination/Flock suspension announced ~July 23–24, 2026.</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>Terminated / Resigned &amp; Criminally Charged</t>
+        </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PRIMARY_ABUSE_TYPE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>FLK-2026-021</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville Police Department</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Three unnamed officers</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Access / Personal Tracking</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Own plates and/or family/acquaintance plates (per agency release)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>During activation/testing of a new internal auditing feature, Fayetteville PD identified license-plate searches inconsistent with authorized use. The department said three employees searched their own plates or those of a family member/acquaintance without a legitimate law-enforcement purpose. All three were placed on administrative leave and later terminated. FPD requested GBI criminal investigation; names not disclosed; no charges announced at termination reporting.</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>New internal auditing feature activation/testing</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Three officers terminated (July 2026); GBI criminal investigation requested; charges not announced in initial reporting.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville PD statement / Atlanta News First / AJC / The Citizen</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlantanewsfirst.com/2026/07/17/3-fayetteville-police-officers-fired-accused-misusing-flock-camera-system/</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Agency news release and ANF/AJC/Citizen Jul 17–18 2026 coverage. Officers unnamed.</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Firings announced ~July 17, 2026.</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Terminated / Resigned (Employment Fallout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FLK-2026-022</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Henry County Police Department</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Patrick Isbell</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Unauthorized Access / Personal Tracking</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Accessed retained license plate data for non–law-enforcement purposes (per agency)</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Henry County Police fired and arrested officer Patrick Isbell, 41, charged with misuse of license plate data on July 10, 2026 after an internal audit found he accessed the department’s Flock network and used retained plate data for non–law-enforcement purposes. Investigation ongoing. Allegations/charges, not a conviction.</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Internal audit</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Fired and arrested; charged with misuse of license plate data (July 10, 2026); investigation ongoing.</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>AJC (July 2026 Georgia wave coverage)</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ajc.com/news/2026/07/3-more-georgia-police-officers-fired-over-alleged-flock-camera-misuse/</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>AJC names Isbell, July 10 charge, Henry County internal audit finding.</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>Charge date July 10, 2026 per AJC.</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>Terminated / Resigned &amp; Criminally Charged</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>FLK-2026-023</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>DeKalb County Sheriff’s Office</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Sgt. Kabiru Salawu</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Access / Personal Tracking</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Flock use (specific search details not released in initial reporting)</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>DeKalb County Sheriff’s Office fired and arrested Sgt. Kabiru Salawu, a ~17-year veteran, after an internal probe identified alleged misuse of Flock license plate reader technology. Charged with misuse of license plate data and felony violation of oath of office. Specific search targets not detailed in initial agency/press coverage. Allegations/charges, not a conviction.</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Internal probe</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Terminated and arrested (July 2026); charged with misuse of license plate data and violation of oath.</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>DeKalb County SO announcement / USA Today / AJC / Reason</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.usatoday.com/story/news/state/georgia/atlanta/2026/07/21/veteran-atlanta-deputy-adds-to-growing-list-of-ga-cops-misusing-flock/90992565007/</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>USA Today / AJC / Reason late July 2026 name Salawu and charges.</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Arrest/firing reported ~July 18–21, 2026.</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Terminated / Resigned &amp; Criminally Charged</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>FLK-2026-024</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Conyers Police Department (Real-Time Crime Center)</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Paige Forte (dispatcher / RTCC supervisor)</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TIME_SPAN_COVERED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2020 - 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DEDUPLICATION_NOTE</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Corpus is N=39 unique cases. Removed FLK-2024-031 as duplicate of FLK-2026-011.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>YEAR_DEFINITION</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Year (and Case_ID year prefix) is the canonical chronology key for this database: the year assigned when the case was first catalogued, usually the year of public disclosure, charging, or Case_ID issuance. It is NOT always identical to the year the underlying ALPR queries occurred. Use Incident_Year for the abuse/window year and Resolution_Year for arrest / plea / conviction / termination when known.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PERCENT_ROUNDING_NOTE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Percentages shown to 1 decimal place; largest share adjusted so category/year/state/outcome tables sum to 100.0%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PUBLIC_FLOCK_CONFIRMED_CASES</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PUBLIC_OTHER_OR_UNCONFIRMED_ALPR</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AGGREGATOR_ALIGNED_STATUS_COUNT</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>flock_named_or_flock_alpr_rows</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>other_or_unconfirmed_alpr_rows</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Do not publish TOTAL_UNIQUE_CASES as “Flock-only.” Some rows are ALPR generally or explicitly “Flock not confirmed.” Aggregator-aligned rows have URLs but are secondary.</t>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>More than 30 Flock accesses April–July 2026 (GBI preliminary)</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>After an internal Flock audit, Conyers PD requested a GBI investigation of RTCC supervisor Paige Forte. Preliminary information indicates she accessed Flock more than 30 times between April and July 2026 for non–law-enforcement purposes; department said inquiries involved her domestic partner’s vehicle to ascertain location. GBI arrested Forte July 22, 2026 and charged Misuse of a License Plate Reader System. Placed on administrative leave pending internal review. Allegations/charges, not a conviction.</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Internal Flock audit; GBI investigation requested by Conyers PD</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Arrested July 22, 2026 (Misuse of a License Plate Reader System); administrative leave; GBI investigation ongoing for DA review.</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>GBI press release (July 23, 2026); Conyers PD / WSB / FOX 5</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>https://gbi.georgia.gov/press-releases/2026-07-23/gbi-arrests-conyers-police-department-employee-misuse-license-plate</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>GBI Jul 23 2026 press release: Forte arrest, &gt;30 accesses Apr–Jul 2026. Partner-tracking detail in Conyers PD / WSB coverage.</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>Arrest July 22, 2026; GBI release July 23.</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>

--- a/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
+++ b/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
@@ -471,7 +471,7 @@
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="48" customWidth="1" min="18" max="18"/>
-    <col width="47" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -837,7 +837,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>ALPR/GPS misuse documented Jan 2024–Jan 2025; felony misconduct charges filed July 2026. Canonical Year=2026 matches Case_ID / charging year.</t>
+          <t>ALPR/GPS misuse documented Jan 2024 to Jan 2025; felony misconduct charges filed July 2026. Canonical Year=2026 matches Case_ID / charging year.</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Released / No Charges — Documented False Stop</t>
+          <t>Released / No Charges: Documented False Stop</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Former Oak Ridge PD Officer Zachary Gauthier accessed the Flock ALPR system 18 times for personal (non-law-enforcement) use between February 25 and March 25, 2025, and also misused Accurint, the State Link System, and his patrol-car computer. An Anderson County Grand Jury indicted him on 23 counts of official misconduct (Class E felony) on July 1, 2025—18 counts specifically for Flock misuse. He was placed on leave April 21, 2025, fired April 24, 2025, and pleaded guilty to all 23 counts on March 23, 2026 (48 hours custody, supervised probation, POST surrender, judicial diversion eligibility). Oak Ridge shares Flock data within the same East Tennessee network as Maryville.</t>
+          <t>Former Oak Ridge PD Officer Zachary Gauthier accessed the Flock ALPR system 18 times for personal (non-law-enforcement) use between February 25 and March 25, 2025, and also misused Accurint, the State Link System, and his patrol-car computer. An Anderson County Grand Jury indicted him on 23 counts of official misconduct (Class E felony) on July 1, 2025: 18 counts specifically for Flock misuse. He was placed on leave April 21, 2025, fired April 24, 2025, and pleaded guilty to all 23 counts on March 23, 2026 (48 hours custody, supervised probation, POST surrender, judicial diversion eligibility). Oak Ridge shares Flock data within the same East Tennessee network as Maryville.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Year/Case_ID keyed to 2025 indictment/public charging; Incident_Year is Feb–Mar 2025 Flock queries; Resolution_Year is Mar 2026 guilty plea.</t>
+          <t>Year/Case_ID keyed to 2025 indictment/public charging; Incident_Year is Feb to Mar 2025 Flock queries; Resolution_Year is Mar 2026 guilty plea.</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>IJ + local reporting: Shelby County Dep. Thadius Gordon; 100+ ALPR tracks of ex-wife; relieved of duty. Primary local coverage describes SCSO plate databases — do not assert Flock without a primary vendor source.</t>
+          <t>IJ + local reporting: Shelby County Dep. Thadius Gordon; 100+ ALPR tracks of ex-wife; relieved of duty. Primary local coverage describes SCSO plate databases, do not assert Flock without a primary vendor source.</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>WESH/WFTV/ClickOrlando Jul 23–24 2026: arrest, termination, Flock suspension. Allegations pending.</t>
+          <t>WESH/WFTV/ClickOrlando Jul 23 to 24 2026: arrest, termination, Flock suspension. Allegations pending.</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -4380,7 +4380,7 @@
       <c r="Q43" s="3" t="inlineStr"/>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>Arrest/termination/Flock suspension announced ~July 23–24, 2026.</t>
+          <t>Arrest/termination/Flock suspension announced ~July 23 to 24, 2026.</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Agency news release and ANF/AJC/Citizen Jul 17–18 2026 coverage. Officers unnamed.</t>
+          <t>Agency news release and ANF/AJC/Citizen Jul 17 to 18 2026 coverage. Officers unnamed.</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Accessed retained license plate data for non–law-enforcement purposes (per agency)</t>
+          <t>Accessed retained license plate data for non-law-enforcement purposes (per agency)</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Henry County Police fired and arrested officer Patrick Isbell, 41, charged with misuse of license plate data on July 10, 2026 after an internal audit found he accessed the department’s Flock network and used retained plate data for non–law-enforcement purposes. Investigation ongoing. Allegations/charges, not a conviction.</t>
+          <t>Henry County Police fired and arrested officer Patrick Isbell, 41, charged with misuse of license plate data on July 10, 2026 after an internal audit found he accessed the department’s Flock network and used retained plate data for non-law-enforcement purposes. Investigation ongoing. Allegations/charges, not a conviction.</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -4663,7 +4663,7 @@
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Arrest/firing reported ~July 18–21, 2026.</t>
+          <t>Arrest/firing reported ~July 18 to 21, 2026.</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>More than 30 Flock accesses April–July 2026 (GBI preliminary)</t>
+          <t>More than 30 Flock accesses April to July 2026 (GBI preliminary)</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>After an internal Flock audit, Conyers PD requested a GBI investigation of RTCC supervisor Paige Forte. Preliminary information indicates she accessed Flock more than 30 times between April and July 2026 for non–law-enforcement purposes; department said inquiries involved her domestic partner’s vehicle to ascertain location. GBI arrested Forte July 22, 2026 and charged Misuse of a License Plate Reader System. Placed on administrative leave pending internal review. Allegations/charges, not a conviction.</t>
+          <t>After an internal Flock audit, Conyers PD requested a GBI investigation of RTCC supervisor Paige Forte. Preliminary information indicates she accessed Flock more than 30 times between April and July 2026 for non-law-enforcement purposes; department said inquiries involved her domestic partner’s vehicle to ascertain location. GBI arrested Forte July 22, 2026 and charged Misuse of a License Plate Reader System. Placed on administrative leave pending internal review. Allegations/charges, not a conviction.</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>GBI Jul 23 2026 press release: Forte arrest, &gt;30 accesses Apr–Jul 2026. Partner-tracking detail in Conyers PD / WSB coverage.</t>
+          <t>GBI Jul 23 2026 press release: Forte arrest, &gt;30 accesses Apr to Jul 2026. Partner-tracking detail in Conyers PD / WSB coverage.</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">

--- a/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
+++ b/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0392B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF6F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +56,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,4597 +452,4888 @@
   </sheetPr>
   <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="48" customWidth="1" min="18" max="18"/>
+    <col width="46" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Case_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Agency_Jurisdiction</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Subject_Officer_Involved</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>System_Vendor</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Misuse_Abuse_Category</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Documented_Search_Count_Frequency</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Detailed_Summary</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Discovery_Method</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Outcome_Disciplinary_Action</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Reference_Source</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Source_URL</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Verification_Notes</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Incident_Year</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Resolution_Year</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Year_Note</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Outcome_Bucket</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ALPR-2024-030</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Shelby County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Deputy Thadius Gordon</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>ALPR (county database; Flock not confirmed in primary local coverage)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>100+</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Deputy Gordon accessed county ALPR tracking databases more than 100 times to stalk his ex-wife and monitor her vehicular movements across the jurisdiction without law enforcement purpose.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Victim complaint and internal audit</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Relieved of duty by Sheriff's Office; subjected to internal and criminal investigation.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice Nationwide ALPR Stalking Report</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>IJ + local reporting: Shelby County Dep. Thadius Gordon; 100+ ALPR tracks of ex-wife; relieved of duty. Primary local coverage describes SCSO plate databases, do not assert Flock without a primary vendor source.</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Relieved of Duty / Under Investigation</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>FLK-2020-038</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lenexa Police Department</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Police Department Leadership / Patrol Officers</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Retaliation / Political Targeting</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>After citizen Canyen Ashworth published a newspaper op-ed critical of local police cooperation with ICE, police retaliated by linking him to anti-ICE posters put up with glue around town. The Police Chief issued a 'MYOC' (Make Your Own Case) BOLO and utilized ALPR cameras to actively track his vehicle around town to manufacture a reason for a traffic stop.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Open records request by KCUR radio and legal intervention by ACLU of Kansas</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Exposed nationally by ACLU as unconstitutional First Amendment retaliation and mass-surveillance abuse.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>ACLU of Kansas / KCUR Radio Report</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>https://www.aclu.org/news/privacy-technology/tracking-alpr-cameras/alpr-against-op-ed-writer</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>FLK-2020-039</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Aurora Police Department</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>ALPR (In-car / Automated Reader)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Gunpoint Detention</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>An ALPR system erroneously flagged Brittney Gilliam's minivan as a stolen vehicle (matching the plate number of a stolen motorcycle from Montana). Officers conducted a high-risk gunpoint stop, forcing four children (ages 6 to 17) to lie face-down in handcuffs on hot pavement before verifying the obvious vehicle mismatch.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Viral bystander video by Jennifer Wurtz and internal police review</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>City paid $1.9 million settlement to the family; police issued formal apology; state legislature reformed high-risk traffic stop protocols.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>AP News / CBS News Colorado / Institute for Justice</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>https://apnews.com/article/handcuffed-black-girls-colorado-settlement-a7a695839b8841e56b7db0d103cc5ed1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Verified $1.9M Aurora settlement (AP Feb 2024); ALPR plate/state mismatch stop.</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>2020</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>FLK-2021-037</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Westmoreland County</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Officer Michael McSherry</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>ALPR / Automated Systems</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Repeated (Unspecified)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Officer McSherry repeatedly accessed automated license plate reader networks to track the vehicular movements of his estranged wife and several other family members.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Internal police audit and criminal investigation</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Pleaded guilty to criminal stalking charges; stripped of police powers and employment.</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>IJ: Westmoreland Officer Michael McSherry; pleaded guilty to stalking via plate readers of estranged wife/family.</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>2021</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FLK-2022-036</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Kechi Police Department</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Lt. Victor Heiar</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Lt. Heiar abused municipal Flock license plate tracking databases to monitor the movements of his estranged wife without her consent or any criminal investigation.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Victim complaint and internal audit</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Pleaded guilty to criminal computer crime and stalking charges; terminated from police employment.</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>KCUR Radio / Kansas Court Records</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>IJ: Kechi Lt Victor Heiar; Flock track of estranged wife; pleaded guilty (IJ lists 2023 resolution year).</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2023</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Misuse associated with 2022 cataloguing; IJ lists 2023 plea/resolution year.</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>FLK-2023-034</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Costa Mesa Police Department</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Officer Robert Josett</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Multiple (Extended Period)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Officer Josett utilized a Flock camera system to track the movements of his mistress as well as her other romantic interests over an extended period without law enforcement authorization.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Internal affairs audit and complaint</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Pleaded guilty to multiple criminal charges in April 2026; employment terminated.</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice / California Court Records</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>IJ: Costa Mesa Officer Robert Josett; Flock track of mistress; pleaded guilty Apr 2026.</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>Misuse year 2023; pleaded guilty April 2026.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FLK-2023-035</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sedgwick Police Department</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Police Chief Lee Nygaard</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking / Physical Stalking</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Police Chief Nygaard used Flock cameras to track his ex-girlfriend's vehicles 228 times over four months and followed her and her new boyfriend in his police cruiser using real-time location alerts.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Internal investigation and county reporting</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Resigned as Police Chief under investigation; documented by ACLU and Institute for Justice.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>ACLU of Wisconsin / KCUR Report</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://www.aclu-wi.org/news/what-the-flock-police-surveillance-is-ripe-for-abuse/</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>IJ/ACLU-WI: Sedgwick Chief Lee Nygaard; 200+ Flock hits on ex + boyfriend; resigned.</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>FLK-2024-027</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Matteson Police Department</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Officer Jaila Cole-Clark</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Hundreds</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Officer Cole-Clark conducted hundreds of unauthorized searches in the department's Flock Safety database to monitor the daily driving routes of her former domestic partner and that person's new partner.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Internal investigation triggered by complaint; documents obtained via FOIA by stopflock.org</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Officer resigned from the police department during the middle of the internal affairs investigation.</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice Review / stopflock.org FOIA</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>IJ/stopflock.org: Matteson Officer Jaila Cole-Clark; hundreds of Flock searches of former domestic partner; resigned mid-investigation.</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>FLK-2024-028</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Orange City Police Department</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Officer Jarmarus Brown</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>100+</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Officer Brown allegedly used automated license plate readers to stalk his girlfriend and her family members more than 100 times over a seven-month span without any investigative basis.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Internal audit and victim complaint</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Arrested and criminally charged in 2025; terminated from the police department.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>IJ: Orange City Officer Jarmarus Brown; 100+ ALPR hits on girlfriend/family; arrested 2025.</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Misuse window associated with 2024; arrested and criminally charged in 2025.</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>FLK-2024-029</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Riverside County Sheriff's Department</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Deputy Alexander Vanny</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Stalking / Kidnapping Facilitation</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>After being arrested for kidnapping his ex-fiancée, forensic audits revealed Deputy Vanny had used the department's ALPR system to illegally track one of her close friends to monitor their movements and gather intelligence.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Criminal investigation into domestic kidnapping and stalking</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>Convicted by jury in Dec 2025 on multiple felony charges; terminated from Sheriff's Department.</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice / Riverside County DA</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>IJ: Riverside Dep. Alexander Vanny; Flock tracking of ex-fiancée friend after kidnapping arrest; convicted Dec 2025.</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>Underlying conduct associated with 2024; jury conviction Dec 2025.</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>FLK-2024-032</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>York County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Wrongful Stop</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>An automated Flock camera misread alphanumeric characters on a passing license plate, generating an erroneous stolen vehicle alert that resulted in an improper traffic stop of an innocent driver.</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Roadside verification of vehicle registration and VIN</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Driver released; documented in Institute for Justice database of automated license plate reader errors.</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>FLK-2024-033</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Niceville Police Department</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Former Officer Coty Hall</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Co-worker Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Officer Hall utilized the department's Flock camera network to unlawfully track the personal driving routes and movements of a fellow police officer and that officer's spouse.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Internal department audit and complaint</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Pleaded no contest to criminal charges; fired from the police department following arrest.</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice / Florida Court Records</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>IJ: Niceville Officer Coty Hall; Flock tracking of coworker+spouse; pleaded no contest; fired (arrest ~Oct 2025).</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>Misuse discovery/ID year 2024; arrest ~Oct 2025 then plea / termination.</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-018</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Milwaukee Police Department</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Officer Josue Ayala</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Officer Ayala conducted 179 unauthorized searches in the Flock Safety system using a single-word justification ('investigation') to stalk a dating partner (&gt;50 searches) and their ex-partner (&gt;100 searches).</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Victim self-searched license plate on haveibeenflocked.com and reported unauthorized police hits to MPD</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Charged with attempted misconduct in public office; pleaded guilty; resigned from MPD.</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>The Marshall Project / Novara Media Investigation</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Marshall Project / Urban Milwaukee / IJ: Ayala ~179 Flock searches of dating partner + ex; charged; pleaded; resigned.</t>
         </is>
       </c>
-      <c r="P14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-019</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Braselton Police Department</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Police Chief Michael Steffman</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Police Chief Steffman abused municipal license plate reader databases to actively track, stalk, and harass multiple people, including a former romantic partner.</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Georgia Bureau of Investigation (GBI) criminal probe</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>Resigned as Police Chief in Nov 2025; arrested by GBI on criminal stalking and misconduct charges.</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / GBI Report (Nov 2025)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>AJC/GBI: Braselton Chief Michael Steffman; ALPR misuse + stalking/harassment; resigned then arrested.</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-020</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Coffee County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Former Deputy Chris Rozar</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Deputy Rozar utilized the department's Flock Safety ALPR database to monitor the movements of a woman he was romantically interested in, tracking her vehicle locations without her consent or any active criminal case.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Victim complaint and subsequent internal investigation</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Fired from the department at the onset of the investigation; criminally charged with multiple offenses.</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / Institute for Justice</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>IJ/AJC: Coffee County former Dep. Chris Rozar charged after Flock stalking of romantic interest; fired.</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-021</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Echols County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Anna Altobello (Civilian Secretary)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Personal Tracking / Stalking</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Multiple (8 Felony Counts)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>A civilian secretary at the sheriff's office accessed the agency's Flock Safety account on multiple occasions for non-law enforcement purposes, conducting unauthorized tag searches on two acquaintances.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Sheriff requested GBI investigation following an external tip</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Arrested by GBI; charged with 8 counts of Misuse of License Plate Data, Stalking, Family Violence Stalking, and Violation of Oath of Office.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / GBI Investigation</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-022</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Columbine Valley Police Department</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Sgt. Jamie Milliman</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Wrongful Accusation / Flawed AI Evidence</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Sgt. Milliman relied blindly on a Flock ALPR camera hit to accuse Denver resident Chrisanna Elser of stealing a $25 package. Police issued a criminal summons without verifying obvious discrepancies. Elser had to obtain her own vehicle's onboard Rivian video to prove she was miles away when the theft occurred.</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Victim presented video alibi proving the Flock hit and police accusation completely false</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Criminal summons voided after Elser provided exculpatory GPS/video evidence; formal disciplinary action / training ordered for Sgt. Milliman per reporting.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>The Colorado Sun / 404 Media Investigation</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>https://coloradosun.com/2025/10/28/flock-camera-police-colorado-columbine-valley/</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Colorado Sun Oct 28 2025 (and Nov discipline follow-ups): Sgt Milliman / Chrisanna Elser wrongful package-theft summons via Flock; summons voided; reprimand + training.</t>
         </is>
       </c>
-      <c r="P18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Summons Voided / Officer Discipline</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-023</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>KY</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Louisville Metro Police Department</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Officer Roberto Cedeno</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Hundreds</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Officer Cedeno utilized the city's automated license plate reader system to track an ex-partner and her friends hundreds of times over a two-month period without any legitimate law enforcement objective.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Internal affairs audit and victim reporting</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>Resigned April 2025 before termination proceedings finished; indicted on multiple felony charges including stalking and unlawful computer access (Courier Journal / LMPD).</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice Nationwide ALPR Review</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>IJ: Louisville Officer Roberto Cedeno charged after ALPR tracking of ex + friends hundreds of times.</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t>Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-024</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>King County Sheriff's Office / Covington</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Deputy Welch</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Excessive Force</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Deputy Welch received a false Flock Safety alert for a stolen van, drove to a gas station, and tackled an innocent man to the ground, grabbing his waist and forcing him face-down onto pavement in a violent wrongful detention.</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>King County Office of Law Enforcement Oversight (OLEO) independent investigation</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Formal oversight investigation confirming lack of probable cause and reliance on unverified Flock alert.</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>King County OLEO Investigation Report #2025-006</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>https://cdn.kingcounty.gov/-/media/king-county/independent/governance-and-leadership/government-oversight/office-of-law-enforcement-oversight/investigation-findings-memos/2026/oleo2025-006-fir.pdf</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-025</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>City of El Cajon</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>City Police Department / Municipal Leadership</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Illegal Data Sharing / Mass Surveillance</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Systemic (Continuous)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>The City of El Cajon systematically violated California law by sharing Flock ALPR data feeds with out-of-state police agencies and federal border/immigration authorities without required legal guardrails or statutory oversight.</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Investigation by California Office of the Attorney General</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>California Attorney General Rob Bonta filed a formal lawsuit against the City of El Cajon in Oct 2025 to halt illegal ALPR data sharing.</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>California Attorney General Lawsuit / CalECPA (Oct 2025)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>https://www.classlawgroup.com/flock-safety-license-plate-reader-cameras-lawsuit</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>FLK-2025-026</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Buford City Schools Police Department</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>School Police Officers</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Mission Creep / Low-Level Surveillance</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>375+</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Between Jan 2025 and March 2026, school police ran more than 375 searches in ALPR tracking databases for low-level 'school residency verification' (RV), representing severe surveillance mission creep without criminal predicate.</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Electronic Frontier Foundation (EFF) nationwide audit log analysis</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Exposed nationally by EFF as an unchecked administrative shortcut around legal due process.</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Electronic Frontier Foundation (EFF) Deep Links Investigation</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>https://www.eff.org/deeplinks/2026/05/more-license-plate-reader-mission-creep-school-residency-verification-background</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>FLK-2025-027</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Oak Ridge Police Department</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Officer Zachary D. Gauthier</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>18 (Flock-specific counts of 23 total)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Former Oak Ridge PD Officer Zachary Gauthier accessed the Flock ALPR system 18 times for personal (non-law-enforcement) use between February 25 and March 25, 2025, and also misused Accurint, the State Link System, and his patrol-car computer. An Anderson County Grand Jury indicted him on 23 counts of official misconduct (Class E felony) on July 1, 2025: 18 counts specifically for Flock misuse. He was placed on leave April 21, 2025, fired April 24, 2025, and pleaded guilty to all 23 counts on March 23, 2026 (48 hours custody, supervised probation, POST surrender, judicial diversion eligibility). Oak Ridge shares Flock data within the same East Tennessee network as Maryville.</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Internal Oak Ridge PD complaints referred to Anderson County District Attorney General Dave Clark for independent investigation</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>Terminated April 24, 2025; indicted July 1, 2025 on 23 counts of official misconduct; pleaded guilty March 23, 2026; sentenced March 2026 to two years on each count with 48 hours to serve, remainder suspended probation, judicial diversion eligibility (3B Media / WATE).</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>WBIR 10News / WATE 6 News / WVLT / Maryville Residents for Privacy / Anderson County DA</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>https://www.wbir.com/article/news/crime/da-former-oak-ridge-officer-pleads-guilty-23-counts-of-misconduct/51-c7b250d6-0843-4407-a0e2-2ecc68c2809a</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>Documented on maryvilleprivacy.org (East TN regional Flock network context). Corroborated by WBIR indictment/plea coverage, WATE indictment detail (18 Flock counts), WVLT plea reporting (Mar 23, 2026), and Anderson County Grand Jury / DA Clark statements.</t>
         </is>
       </c>
-      <c r="P23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>Year/Case_ID keyed to 2025 indictment/public charging; Incident_Year is Feb to Mar 2025 Flock queries; Resolution_Year is Mar 2026 guilty plea.</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S23" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-001</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Pasadena Police Department</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Sgt. Michael Palitz</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Co-worker Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Repeated ('Overwhelming Use' Flagged by System)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>An active internal investigation revealed Sgt. Palitz allegedly abused the Pasadena Police Department's Flock Safety license plate reader camera system to track and stalk a female fellow police officer. According to City Council Member Emmanuel Guerrero, the abuse involved such 'overwhelming use' that the automated system itself flagged the account and notified department administrators. Palitz resigned while under active investigation.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Automated system flag / internal notification triggered by overwhelming volume of searches</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Resigned from the police department in July 2026 while under active internal investigation; investigation remains ongoing.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>KPRC 2 Click2Houston Investigative Report (July 10, 2026)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>https://www.click2houston.com/news/local/2026/07/10/pasadena-police-sergeant-resigns-while-under-internal-investigation-council-member-cites-alleged-misuse-of-flock-camer/</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>KPRC 2 Click2Houston Jul 10 2026: Palitz resigned under investigation; Councilmember Guerrero alleges Flock co-worker stalking; Dept confirms investigation continues.</t>
         </is>
       </c>
-      <c r="P24" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-002</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Albany Police Department</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Tytianna Davis, Jade Jackson, Nicholas Richardson, Brittney Smith, Issac Whitus (5 Officers)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Repeated (Unspecified)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>An internal agency audit revealed that five officers repeatedly accessed the city's Flock Safety LPR camera system for personal, non-law enforcement purposes. The officers used automated plate tracking data to monitor individuals without legitimate investigative justification.</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Internal department audit of Flock ALPR search logs; requested GBI investigation</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>All five officers were terminated immediately and arrested by the Georgia Bureau of Investigation (GBI); charged with felony violation of oath of office and misuse of license plate data.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>Georgia Bureau of Investigation (GBI) Official Press Release (July 2026)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>https://gbi.georgia.gov/press-releases/2026-07-06/gbi-arrests-five-former-albany-police-department-officers-misuse-license</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>GBI Jul 6 2026 press release confirms five former Albany officers arrested for Misuse of License Plate Data + Violation of Oath after Flock audit.</t>
         </is>
       </c>
-      <c r="P25" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-003</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Milwaukee Police Department</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Detective Tehrangi Chapman (Internal Affairs)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking / GPS Tracking</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>An Internal Affairs detective assigned to investigate another officer's ALPR stalking case used MPD's Flock camera network 20 times between Jan 2024 and Jan 2025 to stalk two individuals. He logged queries under false justifications like 'training' and 'test', and secretly installed an unauthorized GPS tracking device on one victim's vehicle.</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Victim report to police regarding stalking and discovery of physical GPS device</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Suspended with pay; charged by Milwaukee County DA in July 2026 with felony misconduct in public office and misdemeanor GPS device misuse.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Urban Milwaukee / Milwaukee County criminal complaint (Jul 2026)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>https://urbanmilwaukee.com/2026/07/09/mpd-investigator-in-flock-stalking-case-now-accused-of-own-misuse/</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Urban Milwaukee / FOX6 / TMJ4 Jul 2026: IA Det. Tehrangi Chapman charged with felony misconduct + GPS-device misuse after Flock audit during Ayala investigation; 20 searches logged as training/test.</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>2024-2025</t>
         </is>
       </c>
-      <c r="Q26" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>ALPR/GPS misuse documented Jan 2024 to Jan 2025; felony misconduct charges filed July 2026. Canonical Year=2026 matches Case_ID / charging year.</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-004</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Cherokee County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Lt. Chris Bryant, Sgt. Mike Creeden, Deputy Cynthia Jodesty</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>A self-initiated audit by the agency's Real-Time Intelligence Division uncovered anomalies in Flock search logs involving two supervisors and one deputy. Investigation confirmed all three used LPR cameras to track license plates for personal reasons unrelated to official police duties.</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Internal audit by Real-Time Intelligence Division</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>All three deputies were fired and arrested; charged with felony violation of oath of office and misdemeanor unlawful retention of license plate reader data.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / CBS News Atlanta (June 2026)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/2-more-cherokee-deputies-accused-of-misusing-license-plate-reader-database/</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>AJC Jun 2026: Cherokee deputies Cynthia Jodesty, Lt Chris Bryant, Sgt Mike Creeden fired+charged for non-LE LPR database misuse after audit.</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-005</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Richmond County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Sheriff's Deputy (Unnamed in state report)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Personal Tracking / Unauthorized Search</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>A Richmond County deputy was arrested and charged after an audit revealed they had used the department's automated license plate recognition database for non-law enforcement personal tracking.</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Internal department database audit</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Arrested and criminally charged; employment terminated.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution Statewide ALPR Audit Report (June 2026)</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P28" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-006</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Greene County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Deputy Quinsha Goss</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Personal Tracking / Stalking</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Multiple (Over 3 Months)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>A departmental audit found that Deputy Goss accessed Flock license plate readers to run searches involving at least one license plate for personal reasons over a 3-month period without any law enforcement mandate.</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Internal audit of Flock camera search logs</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>Terminated from employment; arrested and charged with violation of oath of office and misuse of LPR data.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>CBS News Atlanta / Greene County Sheriff's Office (June 2026)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/07/more-georgia-officers-arrested-for-flock-camera-misuse-officials-say/</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr">
         <is>
           <t>AJC Jul 2026: Greene County Dep. Quinsha Goss arrested after Flock audit found unauthorized plate queries.</t>
         </is>
       </c>
-      <c r="P29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-007</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Menasha Police Department</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Officer Cristian Morales</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Officer Morales utilized the city's Flock ALPR camera network to track an ex-girlfriend, running multiple unauthorized searches without legitimate investigative justification.</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Internal department audit and victim reporting</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Placed on administrative leave; criminally charged with felony misconduct in public office in Feb 2026.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>The Marshall Project / Wisconsin Freedom of Information Council</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Marshall Project / IJ: Menasha Officer Cristian Morales; ex-girlfriend complaint; charged misconduct; administrative leave.</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-008</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Bonner Springs Police Department</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Detective Kyle Rector</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Detective Rector allegedly used automated license plate readers to track his estranged wife and two men he suspected were her new romantic partners without law enforcement authorization.</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Internal affairs audit and victim complaint</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>Criminally charged with multiple stalking and computer crime offenses in March 2026.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>KCUR Radio / Institute for Justice Review</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr">
         <is>
           <t>KBI/KCTV/KSHB: Kyle Rector fired Jan 26 2026; charged Mar 2026 incl. Flock/LPR stalking of estranged wife + other offenses.</t>
         </is>
       </c>
-      <c r="P31" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-009</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>San Francisco Police Department</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>SFPD Patrol Officer (Unnamed in report)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Conflict of Interest / Unauthorized Search</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>An officer used SFPD's Flock ALPR system to locate his wife's stolen car for personal reasons, violating department rules regarding conflicts of interest. He then posted an image of the vehicle on social media.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>An officer in a neighboring jurisdiction recognized the unauthorized social media post</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Subjected to formal internal affairs investigation for violating police surveillance protocols in March 2026.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>The San Francisco Standard / The Marshall Project</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Marshall Project: SFPD officer investigated for ALPR search re: wife stolen car / conflict of interest.</t>
         </is>
       </c>
-      <c r="P32" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-010</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>MO</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Joplin Police Department</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Patrol Officer (Unnamed in agency disclosure)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Excessive Tracking</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>395</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>An officer was discovered to have abused the department's Flock Safety database by conducting 395 unauthorized searches on a single license plate without any active investigative case.</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>Investigation and records analysis by local transparency group DeFlock Joplin</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>Officer was formally terminated from the police department in January 2026.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>KCUR Kansas City / DeFlock Joplin Investigation</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P33" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-011</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Monroe County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Sheriff's Deputy Lamar Roman</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Stalking / Unlawful Traffic Stop</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Deputy Roman allegedly used an ALPR system to track and eventually pull over a woman he had met while providing off-duty security on a television set, monitoring her private vehicular movements.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Victim complaint and internal affairs investigation</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Arrested in 2026 and charged with accessing a computer or electronic device without authorization.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Monroe County SO / Local 10 / Law&amp;Crime (Mar 2026)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>https://www.local10.com/news/local/2026/03/10/florida-keys-deputy-arrested-on-computer-crimes-charges/</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Local10 / Law&amp;Crime / 404 Media: Dep. Lamar Eliseo Roman fired+arrested Mar 2026; DAVID/ALPR hotlist + unauthorized stop of woman met on Bad Monkey set. Primary Monroe County case. Canonical Monroe County Lamar Roman record (FLK-2024-031 removed as duplicate of this case).</t>
         </is>
       </c>
-      <c r="P34" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-012</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Prairie Grove &amp; Holiday Hills Police Dept.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Officer / Chief William C. Copp</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>Officer Copp, who simultaneously served as Police Chief of nearby Holiday Hills, abused authorized police access to search Flock ALPR databases for vehicle locations of several former romantic partners and at least one of their new partners.</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Internal police investigation and victim reporting</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>Arrested in 2026 and criminally charged with official misconduct and LPR misuse.</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t>IJ Plate Privacy list: Officer/Chief William C. Copp Prairie Grove/Holiday Hills; arrested for Flock searches of former romantic partners.</t>
         </is>
       </c>
-      <c r="P35" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr">
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-013</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>San Francisco PD &amp; Los Altos PD</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Municipal Operators &amp; Federal Agencies</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Mass Surveillance / Illegal Data Sharing</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>2,600,000+ (Systemic)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>A class action lawsuit revealed that federal immigration and law enforcement agencies accessed SFPD's Flock cameras over 1.6 million times, while Los Altos shared data over 1 million times with out-of-state agencies, violating California statutory privacy laws designed to protect civil liberties and immigrant communities.</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Public records disclosures and class action legal investigation</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Class action lawsuit filed by Gibbs Mura against Flock Safety and municipal operators seeking statutory damages ($2,500/violation) and injunctions.</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Gibbs Mura Class Action Complaint / California Civil Code § 1798.90.54 (April 2026)</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>https://www.classlawgroup.com/flock-safety-license-plate-reader-cameras-lawsuit</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P36" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-014</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>San Diego Police Department</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Detective Gary Gonzales / Patrol Officers</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / False Arrest</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>San Diego police relied on a false Flock hit to arrest Ariel Beltran and Parra at gunpoint inside a cigar lounge for an attempted carjacking 5 miles away. The camera hit occurred before the pursuit began, proving physical impossibility, yet police ignored cell phone location alibis and arrested both men.</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>Defense investigation proving physical alibi and impossible timestamp synchronization</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>Criminal charges dismissed; victims filed formal civil rights tort claims seeking $1.5 million apiece in damages in April 2026.</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>Times of San Diego Legal Investigation (June 2026)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="3" t="inlineStr">
         <is>
           <t>https://timesofsandiego.com/crime/2026/06/07/a-flock-license-plate-reader-linked-a-san-diego-man-to-a-violent-crime-he-was-five-miles-away/</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="3" t="inlineStr">
         <is>
           <t>Times of San Diego Jun 2026: Hugo Parra AI vehicle match false positive; jailed ~1 month; charges dropped.</t>
         </is>
       </c>
-      <c r="P37" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-015</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>MN</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Plymouth Police Department</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / False Stop</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Multi-day Flock tracking; high-risk box-and-pin stop June 28, 2026</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Automotive journalist Joel Feder and his wife were boxed in by four Plymouth PD squad cars outside a Kohl's after Flock ALPR alerts on a Range Rover press loaner. Police had tracked the vehicle for days via Flock. Root cause: a lost NJ manufacturer plate reported in California was entered into NCIC incomplete as 34 DTM (missing small middle digits); Feder's plate was 34 10 DTM, and Flock OCR also missed those characters. VIN clean; original plate was lost, not stolen; ~1 hour detention.</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Roadside verification (VIN/plate); Plymouth PD statement; Feder first-person account; local TV body-cam reporting</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Released at scene without charges; Plymouth PD attributed alerts to incomplete NCIC entry; Flock stated it was reviewing the incident.</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>The Drive (Feder) / FOX 9 Minneapolis / CBS Minnesota</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>https://www.thedrive.com/news/how-flock-cameras-wrongly-tracked-me-for-days-over-stolen-plates-and-sent-police-after-me</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Primary: Feder The Drive first-person. Local TV: FOX 9 (https://www.fox9.com/news/minnesota-car-reviewer-flock-camera) and CBS Minnesota/WCCO (https://www.cbsnews.com/minnesota/news/flock-cameras-wrongly-flag-plates-as-stolen/). Cross-listed as AI Wrongful Enforcement Database ID 42.</t>
         </is>
       </c>
-      <c r="P38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>Incident late June 2026 (NCIC entry June 24; Flock alerts June 26 and June 28 stop).</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>Released / No Charges: Documented False Stop</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-016</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Cherry Hills Village Police Dept.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Wrongful Stop</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>Flock Safety camera data led police to conduct an improper traffic stop on an innocent driver due to character misinterpretation and database synchronization errors.</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>Roadside investigation and license plate verification</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>Driver released without charges; documented in national civil rights review of ALPR accuracy failures.</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="3" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" s="3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P39" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr">
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-017</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sherwood Police Department</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Gunpoint Detention</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>A Flock camera misread the license plate of an SUV, leading officers to detain an innocent couple at gunpoint while their six-week-old baby sat alone in a car seat in the back of the vehicle.</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Roadside verification after armed detention</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Officers admitted the AI camera error on scene ('I'm not gonna say they're completely perfect...'); documented in national civil rights review.</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P40" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-018</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Baytown Police Department</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Unnamed officer (not publicly identified)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Allegations under investigation (count not public)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>In late July 2026, Baytown Police Chief John Stringer announced allegations that one officer misused the city’s Flock Safety license plate reader system. Stringer authorized an internal affairs investigation and a separate criminal investigation, and asked the Harris County District Attorney’s Office to assist. Chron reported August 2, 2026 that the officer resigned amid the open investigation. The officer has not been publicly named; allegations, not a finding of guilt.</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>Agency receipt of allegations; chief public announcement; DA referral</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>Officer resigned amid open internal and criminal investigations (reported Aug. 2, 2026); Harris County DA assisting; no public disposition naming the officer.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>KPRC 2 / Click2Houston; ABC13; Houston Chronicle; Chron (Aug. 2, 2026)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" s="3" t="inlineStr">
         <is>
           <t>https://www.click2houston.com/news/local/2026/07/27/baytown-police-investigating-officer-accused-of-misusing-flock-license-plate-reader-system/</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>Chief Stringer public statement and DA referral confirmed in KPRC 2 / ABC13 / Chronicle; Chron Aug 2 Houston-area cluster notes resignation. Officer unnamed.</t>
         </is>
       </c>
-      <c r="P41" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R41" t="inlineStr">
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t>Announced late July 2026; resignation reported Aug. 2, 2026; probes ongoing.</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S41" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-019</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Greer Police Department</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Kareem Lynch; Sebastian Echeverry</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Repeated unauthorized searches (per separation documents summarized in reporting)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Greer Police terminated Kareem Lynch (June 26, 2026) and Sebastian Echeverry (June 29, 2026) after an internal investigation alleged unauthorized Flock searches. Reporting on separation documents says Lynch searched plates of an officer he had previously been in a relationship with and entered inaccurate reasons; Echeverry allegedly searched multiple plates and falsely entered “Alcohol Offense Non-DUI.” Department said no criminal charges. Allegations from IA, not court findings.</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Internal investigation; separation documents described in Greenville Online reporting</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Both officers terminated (June 2026); no criminal charges announced per department.</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Greenville Online (July 24, 2026)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>https://www.greenvilleonline.com/story/news/crime/2026/07/24/greer-pd-flock-scandal-upstate-police-oversight/90994284007/</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Greenville Online Jul 24 2026 names Lynch and Echeverry terminations and alleged false search reasons.</t>
         </is>
       </c>
-      <c r="P42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R42" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>Terminations late June 2026; public reporting July 24.</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-020</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Sumter County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Detective Brandy Almany</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Multiple restricted-database lookups alleged (Flock + DAVID + CCIS)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>Sumter County Sheriff’s Office announced an internal audit flagged Det. Brandy Almany’s use of restricted databases. Agency alleges she used Flock ALPR, Florida’s DAVID, and CCIS to obtain information about her husband’s ex-wife for personal reasons, and used unrelated case numbers / false electronic records to make searches appear investigative. Arrested on official misconduct and computer-related charges and terminated. Sheriff Patrick Breeden ordered a complete internal audit and suspended the agency’s use of Flock pending review. Allegations, not a finding of guilt.</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Internal audit of restricted databases; sheriff public statement</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>Arrested and terminated (July 2026); agency suspended Flock use during audit; charges pending.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>WESH 2; WFTV 9; ClickOrlando / News 6</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" s="3" t="inlineStr">
         <is>
           <t>https://www.wesh.com/article/sumter-detective-arrested-database-misuse/73251430</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O43" s="3" t="inlineStr">
         <is>
           <t>WESH/WFTV/ClickOrlando Jul 23 to 24 2026: arrest, termination, Flock suspension. Allegations pending.</t>
         </is>
       </c>
-      <c r="P43" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R43" t="inlineStr">
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t>Arrest/termination/Flock suspension announced ~July 23 to 24, 2026.</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S43" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-021</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fayetteville Police Department</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Three unnamed officers</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Own plates and/or family/acquaintance plates (per agency release)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>During activation/testing of a new internal auditing feature, Fayetteville PD identified license-plate searches inconsistent with authorized use. The department said three employees searched their own plates or those of a family member/acquaintance without a legitimate law-enforcement purpose. All three were placed on administrative leave and later terminated. FPD requested GBI criminal investigation; names not disclosed; no charges announced at termination reporting.</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>New internal auditing feature activation/testing</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Three officers terminated (July 2026); GBI criminal investigation requested; charges not announced in initial reporting.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Fayetteville PD statement / Atlanta News First / AJC / The Citizen</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>https://www.atlantanewsfirst.com/2026/07/17/3-fayetteville-police-officers-fired-accused-misusing-flock-camera-system/</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Agency news release and ANF/AJC/Citizen Jul 17 to 18 2026 coverage. Officers unnamed.</t>
         </is>
       </c>
-      <c r="P44" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R44" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>Firings announced ~July 17, 2026.</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-022</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Henry County Police Department</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Patrick Isbell</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Accessed retained license plate data for non-law-enforcement purposes (per agency)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>Henry County Police fired and arrested officer Patrick Isbell, 41, charged with misuse of license plate data on July 10, 2026 after an internal audit found he accessed the department’s Flock network and used retained plate data for non-law-enforcement purposes. Investigation ongoing. Allegations/charges, not a conviction.</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>Internal audit</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>Fired and arrested; charged with misuse of license plate data (July 10, 2026); investigation ongoing.</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>AJC (July 2026 Georgia wave coverage)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M45" s="3" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/07/3-more-georgia-police-officers-fired-over-alleged-flock-camera-misuse/</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O45" s="3" t="inlineStr">
         <is>
           <t>AJC names Isbell, July 10 charge, Henry County internal audit finding.</t>
         </is>
       </c>
-      <c r="P45" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R45" t="inlineStr">
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
         <is>
           <t>Charge date July 10, 2026 per AJC.</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S45" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-023</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>DeKalb County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Sgt. Kabiru Salawu</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Unauthorized Flock use (specific search details not released in initial reporting)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>DeKalb County Sheriff’s Office fired and arrested Sgt. Kabiru Salawu, a ~17-year veteran, after an internal probe identified alleged misuse of Flock license plate reader technology. Charged with misuse of license plate data and felony violation of oath of office. Specific search targets not detailed in initial agency/press coverage. Allegations/charges, not a conviction.</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Internal probe</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Terminated and arrested (July 2026); charged with misuse of license plate data and violation of oath.</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>DeKalb County SO announcement / USA Today / AJC / Reason</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>https://www.usatoday.com/story/news/state/georgia/atlanta/2026/07/21/veteran-atlanta-deputy-adds-to-growing-list-of-ga-cops-misusing-flock/90992565007/</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>USA Today / AJC / Reason late July 2026 name Salawu and charges.</t>
         </is>
       </c>
-      <c r="P46" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R46" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>Arrest/firing reported ~July 18 to 21, 2026.</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-024</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Conyers Police Department (Real-Time Crime Center)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Paige Forte (dispatcher / RTCC supervisor)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>More than 30 Flock accesses April to July 2026 (GBI preliminary)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>After an internal Flock audit, Conyers PD requested a GBI investigation of RTCC supervisor Paige Forte. Preliminary information indicates she accessed Flock more than 30 times between April and July 2026 for non-law-enforcement purposes; department said inquiries involved her domestic partner’s vehicle to ascertain location. GBI arrested Forte July 22, 2026 and charged Misuse of a License Plate Reader System. Placed on administrative leave pending internal review. Allegations/charges, not a conviction.</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>Internal Flock audit; GBI investigation requested by Conyers PD</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>Arrested July 22, 2026 (Misuse of a License Plate Reader System); administrative leave; GBI investigation ongoing for DA review.</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>GBI press release (July 23, 2026); Conyers PD / WSB / FOX 5</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="3" t="inlineStr">
         <is>
           <t>https://gbi.georgia.gov/press-releases/2026-07-23/gbi-arrests-conyers-police-department-employee-misuse-license-plate</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O47" s="3" t="inlineStr">
         <is>
           <t>GBI Jul 23 2026 press release: Forte arrest, &gt;30 accesses Apr to Jul 2026. Partner-tracking detail in Conyers PD / WSB coverage.</t>
         </is>
       </c>
-      <c r="P47" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R47" t="inlineStr">
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>Arrest July 22, 2026; GBI release July 23.</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S47" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-025</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fort Bend County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Unnamed lieutenant</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>About 148 searches of one plate; about 41 of another (2022–2025)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>Internal-affairs documents obtained by ABC13 and summarized by Chron show a Fort Bend County Sheriff’s Office lieutenant searched one woman’s license plate about 148 times and another plate about 41 times from 2022 through 2025. The lieutenant admitted the searches were not for official sheriff’s-office purposes. The woman reported fearing stalking after checking Have I Been Flocked. Reporting says the agency found a general-orders violation and imposed a two-day suspension.</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Victim complaint after Have I Been Flocked lookup; internal affairs docs</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Found to have violated general orders; two-day suspension reported (ABC13 / Chron). No criminal conviction catalogued here.</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>ABC13; Chron (Aug. 2, 2026 Houston-area cluster)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>https://abc13.com/post/fort-bend-county-sheriffs-office-lieutenant-admits-improper-use-flock-cameras-docs/19528986/</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>ABC13 IA document reporting; Chron Aug 2 cluster corroboration.</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>2022-2025</t>
         </is>
       </c>
-      <c r="Q48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>Search window 2022–2025; discipline reported mid-2026 / Chron Aug 2.</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-026</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Savannah Police Department</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Four officers and two civilian employees (unnamed)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Multiple flagged searches (counts not fully public)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>Savannah Police announced that an internal audit under Flock’s Audit Assistance Program flagged potential misuse by four officers and two civilian employees. All six were placed on administrative leave; discipline up to termination is on the table; cases referred to the Georgia Bureau of Investigation. Alleged searches included personal acquaintances and family members; one officer allegedly shared SPD Flock access with personnel from an outside agency. Internal investigation began July 27, 2026.</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>Flock Audit Assistance / agency Office of Professional Standards audit</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>Six employees on administrative leave; GBI criminal referral; possible termination; investigations ongoing as of early August 2026 reporting.</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>WJCL; WTOC; WRDW</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" s="3" t="inlineStr">
         <is>
           <t>https://www.wjcl.com/article/savannah-police-flock-system-misuse-investigation/73321620</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N49" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="3" t="inlineStr">
         <is>
           <t>SPD / mayor statements carried by WJCL (July 31) and WRDW (Aug 2).</t>
         </is>
       </c>
-      <c r="P49" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R49" t="inlineStr">
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
         <is>
           <t>Leave / GBI referral announced July 31, 2026; disposition pending.</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S49" s="3" t="inlineStr">
         <is>
           <t>Under Investigation / Pending</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-027</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Charlotte-Mecklenburg Police Department</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Officer Seth Daniel Elliott</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>At least one alleged plate query for a friend (drug target)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>On July 29, 2026, CMPD Officer Seth Daniel Elliott was arrested and charged with illegally accessing a government computer. An SBI affidavit summarized in local reporting says a friend who was the target of a Watauga County drug investigation asked Elliott to run a plate; investigators allege Elliott queried Flock Safety and CJLEADS, learned it belonged to an undercover officer’s vehicle, and relayed that over Snapchat. CMPD placed Elliott on unpaid leave and revoked database access. On August 4, CMPD released its Flock MOU under press pressure: CMPD does not own Flock cameras but gets network access (including limited community devices) via the MOU; the trial period was extended past May.</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>SBI investigation / charging affidavit; local investigative reporting</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>Arrested and charged (illegal access to a government computer); unpaid administrative leave; database access revoked. Allegations / charges, not a conviction.</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>WBTV; Spectrum News; WSOC</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>https://www.wbtv.com/2026/07/30/arrested-charlotte-mecklenburg-police-officer-accused-giving-information-investigation-target/</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>WBTV July 30 arrest story; WBTV Aug 4 MOU release. Charging allegations pending.</t>
         </is>
       </c>
-      <c r="P50" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>Arrest July 29, 2026; MOU released Aug 4, 2026.</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-028</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>OH</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Reynoldsburg Police Department</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Two unnamed officers</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>One officer: 50+ non-work searches over ~6 months (records)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>NBC4 reported August 4, 2026 that two Reynoldsburg Police officers resigned within about two months amid internal reviews of possible Flock misuse. Records described for one officer show more than 50 non-work-related searches over six months; that officer resigned effective July 16, the day before a scheduled administrative review. Chief Curtis Baker said non-law-enforcement use of Flock or other police databases will not be tolerated. Criminal charges were unclear in that reporting.</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>Internal investigation; chief news release after NBC4 inquiry</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>Both officers resigned; possible criminal charges unclear as of Aug. 4, 2026 reporting.</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>NBC4 WCMH-TV (Aug. 4, 2026)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr">
         <is>
           <t>https://www.nbc4i.com/news/local-news/reynoldsburg/reynoldsburg-officer-may-have-misused-flock-cameras-records-show/</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="3" t="inlineStr">
         <is>
           <t>NBC4 Aug 4 reporting quoting Chief Baker release and internal records description.</t>
         </is>
       </c>
-      <c r="P51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R51" t="inlineStr">
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
         <is>
           <t>Resignations reported Aug. 4, 2026 (one effective July 16).</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S51" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>FLK-2026-029</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Habersham County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Deputy Christian Brewer</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Personal-relationship searches (counts not fully public)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Atlanta News First reported July 31, 2026 that Habersham County Deputy Christian Brewer was fired and arrested after allegedly using the department’s Flock license plate reader system for reasons unrelated to his job. The sheriff’s office said the searches involved someone he was in a personal relationship with. Charges reported: one count of felony violation of oath of office and two counts of misdemeanor misuse of license plate data. Allegations and charging documents as reported, not a conviction.</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Flock Audit Assistance / agency internal audit</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Fired and arrested; felony oath-of-office count plus misdemeanor plate-data misuse counts reported (ANF July 31, 2026).</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>Atlanta News First (July 31, 2026)</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>https://www.atlantanewsfirst.com/2026/07/31/habersham-county-deputy-fired-arrested-after-flock-license-plate-reader-audit/</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>ANF Investigates naming Brewer; sheriff Robin Krockum statement quoted.</t>
         </is>
       </c>
-      <c r="P52" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R52" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>Fired and arrested; reported July 31, 2026.</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>FLK-2026-030</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Coweta County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Three unnamed employees</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Accounts flagged in self-initiated audit (details not public)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>On August 4, 2026, the Coweta County Sheriff’s Office said three employees resigned after a self-initiated Flock Safety audit flagged their accounts for additional review. Each resigned during meetings with department leaders before the audit finished and before an internal investigation opened. The agency asked the Georgia Bureau of Investigation to investigate independently and said it would add training for Flock users. Employees were not publicly identified; alleged misuse details were not released.</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>Self-initiated agency Flock audit / Audit Assistance tooling</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>Three employees resigned before internal investigation; GBI independent investigation requested (Aug. 4, 2026 reporting).</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>Atlanta News First; FOX 5 Atlanta; WSB-TV</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>https://www.atlantanewsfirst.com/2026/08/04/3-coweta-county-sheriffs-office-employees-resign-after-flock-audit/</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N53" s="3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O53" s="3" t="inlineStr">
         <is>
           <t>Agency statement carried by ANF / FOX 5 / WSB; names and search details withheld.</t>
         </is>
       </c>
-      <c r="P53" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2026</v>
-      </c>
-      <c r="R53" t="inlineStr">
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
         <is>
           <t>Resignations and GBI referral announced Aug. 4, 2026.</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S53" s="3" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>

--- a/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
+++ b/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5339,6 +5339,99 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>FLK-2026-031</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Bibb County Sheriff’s Office</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Deputies under review (unnamed; three flagged queries)</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Access / Personal Tracking</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Three separate queries flagged by monthly audit algorithm</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>On August 3–4, 2026, the Bibb County Sheriff’s Office said its routine monthly Flock audit returned three separate queries flagged as problematic by Flock’s auditing algorithm. Internal Affairs is reviewing whether any deputies violated policy. Officials said no deputies had been terminated or placed on administrative leave, but those under review had Flock access suspended pending the outcome. The agency said it would publicly disclose confirmed findings of misuse when investigations finish. Allegations under investigation, not findings of guilt.</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Monthly agency Flock audit / Audit Assistance algorithm</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Internal Affairs investigations open; Flock access suspended for deputies under review; no firings or leave announced as of Aug. 3–4 reporting.</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Georgia Public Broadcasting; WGXA; Macon Telegraph; 41NBC</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gpb.org/news/2026/08/04/bibb-county-sheriffs-office-launches-investigation-for-potential-misuse-of-flock</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Agency statement carried by GPB / WGXA / Macon Telegraph / 41NBC; names and query details withheld; investigations active.</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Investigations announced Aug. 3–4, 2026; outcomes pending.</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>Under Investigation / Pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
+++ b/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,30 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C0392B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDF6F6"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,35 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E2E8F0"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,4985 +413,4777 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="48" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="48" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="48" customWidth="1" min="18" max="18"/>
-    <col width="46" customWidth="1" min="19" max="19"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Case_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Agency_Jurisdiction</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subject_Officer_Involved</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>System_Vendor</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Misuse_Abuse_Category</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Documented_Search_Count_Frequency</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Detailed_Summary</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Discovery_Method</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Outcome_Disciplinary_Action</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Reference_Source</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Source_URL</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Verification_Notes</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Incident_Year</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Resolution_Year</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Year_Note</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Outcome_Bucket</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ALPR-2024-030</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Shelby County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Deputy Thadius Gordon</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>ALPR (county database; Flock not confirmed in primary local coverage)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>100+</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Deputy Gordon accessed county ALPR tracking databases more than 100 times to stalk his ex-wife and monitor her vehicular movements across the jurisdiction without law enforcement purpose.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Victim complaint and internal audit</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Relieved of duty by Sheriff's Office; subjected to internal and criminal investigation.</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Institute for Justice Nationwide ALPR Stalking Report</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>IJ + local reporting: Shelby County Dep. Thadius Gordon; 100+ ALPR tracks of ex-wife; relieved of duty. Primary local coverage describes SCSO plate databases, do not assert Flock without a primary vendor source.</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="P2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Relieved of Duty / Under Investigation</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>FLK-2020-038</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Lenexa Police Department</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Police Department Leadership / Patrol Officers</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Retaliation / Political Targeting</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>After citizen Canyen Ashworth published a newspaper op-ed critical of local police cooperation with ICE, police retaliated by linking him to anti-ICE posters put up with glue around town. The Police Chief issued a 'MYOC' (Make Your Own Case) BOLO and utilized ALPR cameras to actively track his vehicle around town to manufacture a reason for a traffic stop.</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Open records request by KCUR radio and legal intervention by ACLU of Kansas</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Exposed nationally by ACLU as unconstitutional First Amendment retaliation and mass-surveillance abuse.</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>ACLU of Kansas / KCUR Radio Report</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>https://www.aclu.org/news/privacy-technology/tracking-alpr-cameras/alpr-against-op-ed-writer</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="P3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>FLK-2020-039</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Aurora Police Department</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>ALPR (In-car / Automated Reader)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Gunpoint Detention</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>An ALPR system erroneously flagged Brittney Gilliam's minivan as a stolen vehicle (matching the plate number of a stolen motorcycle from Montana). Officers conducted a high-risk gunpoint stop, forcing four children (ages 6 to 17) to lie face-down in handcuffs on hot pavement before verifying the obvious vehicle mismatch.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Viral bystander video by Jennifer Wurtz and internal police review</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>City paid $1.9 million settlement to the family; police issued formal apology; state legislature reformed high-risk traffic stop protocols.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>AP News / CBS News Colorado / Institute for Justice</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>https://apnews.com/article/handcuffed-black-girls-colorado-settlement-a7a695839b8841e56b7db0d103cc5ed1</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Verified $1.9M Aurora settlement (AP Feb 2024); ALPR plate/state mismatch stop.</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="P4" t="n">
+        <v>2020</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>FLK-2021-037</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Westmoreland County</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Officer Michael McSherry</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ALPR / Automated Systems</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Repeated (Unspecified)</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Officer McSherry repeatedly accessed automated license plate reader networks to track the vehicular movements of his estranged wife and several other family members.</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Internal police audit and criminal investigation</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Pleaded guilty to criminal stalking charges; stripped of police powers and employment.</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>IJ: Westmoreland Officer Michael McSherry; pleaded guilty to stalking via plate readers of estranged wife/family.</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="P5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>FLK-2022-036</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Kechi Police Department</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Lt. Victor Heiar</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Domestic Stalking</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Lt. Heiar abused municipal Flock license plate tracking databases to monitor the movements of his estranged wife without her consent or any criminal investigation.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Victim complaint and internal audit</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Pleaded guilty to criminal computer crime and stalking charges; terminated from police employment.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>KCUR Radio / Kansas Court Records</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>IJ: Kechi Lt Victor Heiar; Flock track of estranged wife; pleaded guilty (IJ lists 2023 resolution year).</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="P6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>Misuse associated with 2022 cataloguing; IJ lists 2023 plea/resolution year.</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>FLK-2023-034</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Costa Mesa Police Department</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Officer Robert Josett</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Multiple (Extended Period)</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Officer Josett utilized a Flock camera system to track the movements of his mistress as well as her other romantic interests over an extended period without law enforcement authorization.</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Internal affairs audit and complaint</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Pleaded guilty to multiple criminal charges in April 2026; employment terminated.</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Institute for Justice / California Court Records</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>IJ: Costa Mesa Officer Robert Josett; Flock track of mistress; pleaded guilty Apr 2026.</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="P7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Misuse year 2023; pleaded guilty April 2026.</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>FLK-2023-035</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Sedgwick Police Department</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Police Chief Lee Nygaard</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Romantic Stalking / Physical Stalking</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Police Chief Nygaard used Flock cameras to track his ex-girlfriend's vehicles 228 times over four months and followed her and her new boyfriend in his police cruiser using real-time location alerts.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Internal investigation and county reporting</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Resigned as Police Chief under investigation; documented by ACLU and Institute for Justice.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>ACLU of Wisconsin / KCUR Report</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>https://www.aclu-wi.org/news/what-the-flock-police-surveillance-is-ripe-for-abuse/</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>IJ/ACLU-WI: Sedgwick Chief Lee Nygaard; 200+ Flock hits on ex + boyfriend; resigned.</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="P8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>FLK-2024-027</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Matteson Police Department</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Officer Jaila Cole-Clark</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Hundreds</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Officer Cole-Clark conducted hundreds of unauthorized searches in the department's Flock Safety database to monitor the daily driving routes of her former domestic partner and that person's new partner.</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Internal investigation triggered by complaint; documents obtained via FOIA by stopflock.org</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Officer resigned from the police department during the middle of the internal affairs investigation.</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Institute for Justice Review / stopflock.org FOIA</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>IJ/stopflock.org: Matteson Officer Jaila Cole-Clark; hundreds of Flock searches of former domestic partner; resigned mid-investigation.</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="P9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>FLK-2024-028</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Orange City Police Department</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Officer Jarmarus Brown</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>100+</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Officer Brown allegedly used automated license plate readers to stalk his girlfriend and her family members more than 100 times over a seven-month span without any investigative basis.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Internal audit and victim complaint</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Arrested and criminally charged in 2025; terminated from the police department.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>IJ: Orange City Officer Jarmarus Brown; 100+ ALPR hits on girlfriend/family; arrested 2025.</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="P10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Misuse window associated with 2024; arrested and criminally charged in 2025.</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>FLK-2024-029</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Riverside County Sheriff's Department</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Deputy Alexander Vanny</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Stalking / Kidnapping Facilitation</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>After being arrested for kidnapping his ex-fiancée, forensic audits revealed Deputy Vanny had used the department's ALPR system to illegally track one of her close friends to monitor their movements and gather intelligence.</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Criminal investigation into domestic kidnapping and stalking</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Convicted by jury in Dec 2025 on multiple felony charges; terminated from Sheriff's Department.</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Institute for Justice / Riverside County DA</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>IJ: Riverside Dep. Alexander Vanny; Flock tracking of ex-fiancée friend after kidnapping arrest; convicted Dec 2025.</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="P11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>Underlying conduct associated with 2024; jury conviction Dec 2025.</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>FLK-2024-032</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>York County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Wrongful Stop</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>An automated Flock camera misread alphanumeric characters on a passing license plate, generating an erroneous stolen vehicle alert that resulted in an improper traffic stop of an innocent driver.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Roadside verification of vehicle registration and VIN</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Driver released; documented in Institute for Justice database of automated license plate reader errors.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="P12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>FLK-2024-033</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Niceville Police Department</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Former Officer Coty Hall</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Co-worker Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Officer Hall utilized the department's Flock camera network to unlawfully track the personal driving routes and movements of a fellow police officer and that officer's spouse.</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Internal department audit and complaint</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Pleaded no contest to criminal charges; fired from the police department following arrest.</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Institute for Justice / Florida Court Records</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>IJ: Niceville Officer Coty Hall; Flock tracking of coworker+spouse; pleaded no contest; fired (arrest ~Oct 2025).</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="P13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>Misuse discovery/ID year 2024; arrest ~Oct 2025 then plea / termination.</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>FLK-2025-018</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Milwaukee Police Department</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Officer Josue Ayala</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Officer Ayala conducted 179 unauthorized searches in the Flock Safety system using a single-word justification ('investigation') to stalk a dating partner (&gt;50 searches) and their ex-partner (&gt;100 searches).</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Victim self-searched license plate on haveibeenflocked.com and reported unauthorized police hits to MPD</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Charged with attempted misconduct in public office; pleaded guilty; resigned from MPD.</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>The Marshall Project / Novara Media Investigation</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Marshall Project / Urban Milwaukee / IJ: Ayala ~179 Flock searches of dating partner + ex; charged; pleaded; resigned.</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="P14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>FLK-2025-019</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Braselton Police Department</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Police Chief Michael Steffman</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Romantic Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Police Chief Steffman abused municipal license plate reader databases to actively track, stalk, and harass multiple people, including a former romantic partner.</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Georgia Bureau of Investigation (GBI) criminal probe</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Resigned as Police Chief in Nov 2025; arrested by GBI on criminal stalking and misconduct charges.</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / GBI Report (Nov 2025)</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>AJC/GBI: Braselton Chief Michael Steffman; ALPR misuse + stalking/harassment; resigned then arrested.</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="P15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>FLK-2025-020</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Coffee County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Former Deputy Chris Rozar</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Deputy Rozar utilized the department's Flock Safety ALPR database to monitor the movements of a woman he was romantically interested in, tracking her vehicle locations without her consent or any active criminal case.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Victim complaint and subsequent internal investigation</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Fired from the department at the onset of the investigation; criminally charged with multiple offenses.</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / Institute for Justice</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>IJ/AJC: Coffee County former Dep. Chris Rozar charged after Flock stalking of romantic interest; fired.</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="P16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>FLK-2025-021</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Echols County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Anna Altobello (Civilian Secretary)</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Personal Tracking / Stalking</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Multiple (8 Felony Counts)</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>A civilian secretary at the sheriff's office accessed the agency's Flock Safety account on multiple occasions for non-law enforcement purposes, conducting unauthorized tag searches on two acquaintances.</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Sheriff requested GBI investigation following an external tip</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Arrested by GBI; charged with 8 counts of Misuse of License Plate Data, Stalking, Family Violence Stalking, and Violation of Oath of Office.</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / GBI Investigation</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="P17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>FLK-2025-022</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Columbine Valley Police Department</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Sgt. Jamie Milliman</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Wrongful Accusation / Flawed AI Evidence</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Sgt. Milliman relied blindly on a Flock ALPR camera hit to accuse Denver resident Chrisanna Elser of stealing a $25 package. Police issued a criminal summons without verifying obvious discrepancies. Elser had to obtain her own vehicle's onboard Rivian video to prove she was miles away when the theft occurred.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Victim presented video alibi proving the Flock hit and police accusation completely false</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Criminal summons voided after Elser provided exculpatory GPS/video evidence; formal disciplinary action / training ordered for Sgt. Milliman per reporting.</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>The Colorado Sun / 404 Media Investigation</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>https://coloradosun.com/2025/10/28/flock-camera-police-colorado-columbine-valley/</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Colorado Sun Oct 28 2025 (and Nov discipline follow-ups): Sgt Milliman / Chrisanna Elser wrongful package-theft summons via Flock; summons voided; reprimand + training.</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="P18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Summons Voided / Officer Discipline</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>FLK-2025-023</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>KY</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Louisville Metro Police Department</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Officer Roberto Cedeno</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Hundreds</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Officer Cedeno utilized the city's automated license plate reader system to track an ex-partner and her friends hundreds of times over a two-month period without any legitimate law enforcement objective.</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Internal affairs audit and victim reporting</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Resigned April 2025 before termination proceedings finished; indicted on multiple felony charges including stalking and unlawful computer access (Courier Journal / LMPD).</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Institute for Justice Nationwide ALPR Review</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>IJ: Louisville Officer Roberto Cedeno charged after ALPR tracking of ex + friends hundreds of times.</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr">
+      <c r="P19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>FLK-2025-024</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>King County Sheriff's Office / Covington</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Deputy Welch</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Excessive Force</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Deputy Welch received a false Flock Safety alert for a stolen van, drove to a gas station, and tackled an innocent man to the ground, grabbing his waist and forcing him face-down onto pavement in a violent wrongful detention.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>King County Office of Law Enforcement Oversight (OLEO) independent investigation</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Formal oversight investigation confirming lack of probable cause and reliance on unverified Flock alert.</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>King County OLEO Investigation Report #2025-006</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>https://cdn.kingcounty.gov/-/media/king-county/independent/governance-and-leadership/government-oversight/office-of-law-enforcement-oversight/investigation-findings-memos/2026/oleo2025-006-fir.pdf</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="P20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>FLK-2025-025</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>City of El Cajon</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>City Police Department / Municipal Leadership</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Illegal Data Sharing / Mass Surveillance</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Systemic (Continuous)</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>The City of El Cajon systematically violated California law by sharing Flock ALPR data feeds with out-of-state police agencies and federal border/immigration authorities without required legal guardrails or statutory oversight.</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Investigation by California Office of the Attorney General</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>California Attorney General Rob Bonta filed a formal lawsuit against the City of El Cajon in Oct 2025 to halt illegal ALPR data sharing.</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>California Attorney General Lawsuit / CalECPA (Oct 2025)</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>https://www.classlawgroup.com/flock-safety-license-plate-reader-cameras-lawsuit</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="P21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>FLK-2025-026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Buford City Schools Police Department</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>School Police Officers</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Mission Creep / Low-Level Surveillance</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>375+</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Between Jan 2025 and March 2026, school police ran more than 375 searches in ALPR tracking databases for low-level 'school residency verification' (RV), representing severe surveillance mission creep without criminal predicate.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Electronic Frontier Foundation (EFF) nationwide audit log analysis</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Exposed nationally by EFF as an unchecked administrative shortcut around legal due process.</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Electronic Frontier Foundation (EFF) Deep Links Investigation</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>https://www.eff.org/deeplinks/2026/05/more-license-plate-reader-mission-creep-school-residency-verification-background</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="P22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>FLK-2025-027</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="B23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Oak Ridge Police Department</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Officer Zachary D. Gauthier</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>18 (Flock-specific counts of 23 total)</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Former Oak Ridge PD Officer Zachary Gauthier accessed the Flock ALPR system 18 times for personal (non-law-enforcement) use between February 25 and March 25, 2025, and also misused Accurint, the State Link System, and his patrol-car computer. An Anderson County Grand Jury indicted him on 23 counts of official misconduct (Class E felony) on July 1, 2025: 18 counts specifically for Flock misuse. He was placed on leave April 21, 2025, fired April 24, 2025, and pleaded guilty to all 23 counts on March 23, 2026 (48 hours custody, supervised probation, POST surrender, judicial diversion eligibility). Oak Ridge shares Flock data within the same East Tennessee network as Maryville.</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Internal Oak Ridge PD complaints referred to Anderson County District Attorney General Dave Clark for independent investigation</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Terminated April 24, 2025; indicted July 1, 2025 on 23 counts of official misconduct; pleaded guilty March 23, 2026; sentenced March 2026 to two years on each count with 48 hours to serve, remainder suspended probation, judicial diversion eligibility (3B Media / WATE).</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>WBIR 10News / WATE 6 News / WVLT / Maryville Residents for Privacy / Anderson County DA</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>https://www.wbir.com/article/news/crime/da-former-oak-ridge-officer-pleads-guilty-23-counts-of-misconduct/51-c7b250d6-0843-4407-a0e2-2ecc68c2809a</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Documented on maryvilleprivacy.org (East TN regional Flock network context). Corroborated by WBIR indictment/plea coverage, WATE indictment detail (18 Flock counts), WVLT plea reporting (Mar 23, 2026), and Anderson County Grand Jury / DA Clark statements.</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
+      <c r="P23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>Year/Case_ID keyed to 2025 indictment/public charging; Incident_Year is Feb to Mar 2025 Flock queries; Resolution_Year is Mar 2026 guilty plea.</t>
         </is>
       </c>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>FLK-2026-001</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Pasadena Police Department</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Sgt. Michael Palitz</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Co-worker Stalking / Harassment</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Repeated ('Overwhelming Use' Flagged by System)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>An active internal investigation revealed Sgt. Palitz allegedly abused the Pasadena Police Department's Flock Safety license plate reader camera system to track and stalk a female fellow police officer. According to City Council Member Emmanuel Guerrero, the abuse involved such 'overwhelming use' that the automated system itself flagged the account and notified department administrators. Palitz resigned while under active investigation.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Automated system flag / internal notification triggered by overwhelming volume of searches</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Resigned from the police department in July 2026 while under active internal investigation; investigation remains ongoing.</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>KPRC 2 Click2Houston Investigative Report (July 10, 2026)</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>https://www.click2houston.com/news/local/2026/07/10/pasadena-police-sergeant-resigns-while-under-internal-investigation-council-member-cites-alleged-misuse-of-flock-camer/</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>KPRC 2 Click2Houston Jul 10 2026: Palitz resigned under investigation; Councilmember Guerrero alleges Flock co-worker stalking; Dept confirms investigation continues.</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="P24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>FLK-2026-002</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Albany Police Department</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Tytianna Davis, Jade Jackson, Nicholas Richardson, Brittney Smith, Issac Whitus (5 Officers)</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Repeated (Unspecified)</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>An internal agency audit revealed that five officers repeatedly accessed the city's Flock Safety LPR camera system for personal, non-law enforcement purposes. The officers used automated plate tracking data to monitor individuals without legitimate investigative justification.</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Internal department audit of Flock ALPR search logs; requested GBI investigation</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>All five officers were terminated immediately and arrested by the Georgia Bureau of Investigation (GBI); charged with felony violation of oath of office and misuse of license plate data.</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Georgia Bureau of Investigation (GBI) Official Press Release (July 2026)</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>https://gbi.georgia.gov/press-releases/2026-07-06/gbi-arrests-five-former-albany-police-department-officers-misuse-license</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>GBI Jul 6 2026 press release confirms five former Albany officers arrested for Misuse of License Plate Data + Violation of Oath after Flock audit.</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="P25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>FLK-2026-003</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Milwaukee Police Department</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Detective Tehrangi Chapman (Internal Affairs)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Romantic Stalking / GPS Tracking</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>An Internal Affairs detective assigned to investigate another officer's ALPR stalking case used MPD's Flock camera network 20 times between Jan 2024 and Jan 2025 to stalk two individuals. He logged queries under false justifications like 'training' and 'test', and secretly installed an unauthorized GPS tracking device on one victim's vehicle.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Victim report to police regarding stalking and discovery of physical GPS device</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Suspended with pay; charged by Milwaukee County DA in July 2026 with felony misconduct in public office and misdemeanor GPS device misuse.</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Urban Milwaukee / Milwaukee County criminal complaint (Jul 2026)</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>https://urbanmilwaukee.com/2026/07/09/mpd-investigator-in-flock-stalking-case-now-accused-of-own-misuse/</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Urban Milwaukee / FOX6 / TMJ4 Jul 2026: IA Det. Tehrangi Chapman charged with felony misconduct + GPS-device misuse after Flock audit during Ayala investigation; 20 searches logged as training/test.</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>2024-2025</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="Q26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>ALPR/GPS misuse documented Jan 2024 to Jan 2025; felony misconduct charges filed July 2026. Canonical Year=2026 matches Case_ID / charging year.</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>FLK-2026-004</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="B27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Cherokee County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Lt. Chris Bryant, Sgt. Mike Creeden, Deputy Cynthia Jodesty</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>A self-initiated audit by the agency's Real-Time Intelligence Division uncovered anomalies in Flock search logs involving two supervisors and one deputy. Investigation confirmed all three used LPR cameras to track license plates for personal reasons unrelated to official police duties.</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Internal audit by Real-Time Intelligence Division</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>All three deputies were fired and arrested; charged with felony violation of oath of office and misdemeanor unlawful retention of license plate reader data.</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution / CBS News Atlanta (June 2026)</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/2-more-cherokee-deputies-accused-of-misusing-license-plate-reader-database/</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>AJC Jun 2026: Cherokee deputies Cynthia Jodesty, Lt Chris Bryant, Sgt Mike Creeden fired+charged for non-LE LPR database misuse after audit.</t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="P27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>FLK-2026-005</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Richmond County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Sheriff's Deputy (Unnamed in state report)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Personal Tracking / Unauthorized Search</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>A Richmond County deputy was arrested and charged after an audit revealed they had used the department's automated license plate recognition database for non-law enforcement personal tracking.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Internal department database audit</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Arrested and criminally charged; employment terminated.</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Atlanta Journal-Constitution Statewide ALPR Audit Report (June 2026)</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="P28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>FLK-2026-006</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Greene County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Deputy Quinsha Goss</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Personal Tracking / Stalking</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Multiple (Over 3 Months)</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>A departmental audit found that Deputy Goss accessed Flock license plate readers to run searches involving at least one license plate for personal reasons over a 3-month period without any law enforcement mandate.</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Internal audit of Flock camera search logs</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Terminated from employment; arrested and charged with violation of oath of office and misuse of LPR data.</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>CBS News Atlanta / Greene County Sheriff's Office (June 2026)</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/07/more-georgia-officers-arrested-for-flock-camera-misuse-officials-say/</t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>AJC Jul 2026: Greene County Dep. Quinsha Goss arrested after Flock audit found unauthorized plate queries.</t>
         </is>
       </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="P29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>FLK-2026-007</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>WI</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Menasha Police Department</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Officer Cristian Morales</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Officer Morales utilized the city's Flock ALPR camera network to track an ex-girlfriend, running multiple unauthorized searches without legitimate investigative justification.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Internal department audit and victim reporting</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Placed on administrative leave; criminally charged with felony misconduct in public office in Feb 2026.</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>The Marshall Project / Wisconsin Freedom of Information Council</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Marshall Project / IJ: Menasha Officer Cristian Morales; ex-girlfriend complaint; charged misconduct; administrative leave.</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="P30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>FLK-2026-008</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>KS</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Bonner Springs Police Department</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Detective Kyle Rector</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Detective Rector allegedly used automated license plate readers to track his estranged wife and two men he suspected were her new romantic partners without law enforcement authorization.</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Internal affairs audit and victim complaint</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Criminally charged with multiple stalking and computer crime offenses in March 2026.</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>KCUR Radio / Institute for Justice Review</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>KBI/KCTV/KSHB: Kyle Rector fired Jan 26 2026; charged Mar 2026 incl. Flock/LPR stalking of estranged wife + other offenses.</t>
         </is>
       </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr"/>
-      <c r="R31" s="3" t="inlineStr"/>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="P31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>FLK-2026-009</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>San Francisco Police Department</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>SFPD Patrol Officer (Unnamed in report)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Conflict of Interest / Unauthorized Search</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>An officer used SFPD's Flock ALPR system to locate his wife's stolen car for personal reasons, violating department rules regarding conflicts of interest. He then posted an image of the vehicle on social media.</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>An officer in a neighboring jurisdiction recognized the unauthorized social media post</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Subjected to formal internal affairs investigation for violating police surveillance protocols in March 2026.</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>The San Francisco Standard / The Marshall Project</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>https://www.themarshallproject.org/2026/03/07/police-camera-wisconsin-california-colorado</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Marshall Project: SFPD officer investigated for ALPR search re: wife stolen car / conflict of interest.</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="P32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>FLK-2026-010</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>MO</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Joplin Police Department</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Patrol Officer (Unnamed in agency disclosure)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Unauthorized Access / Excessive Tracking</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>395</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>An officer was discovered to have abused the department's Flock Safety database by conducting 395 unauthorized searches on a single license plate without any active investigative case.</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Investigation and records analysis by local transparency group DeFlock Joplin</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Officer was formally terminated from the police department in January 2026.</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>KCUR Kansas City / DeFlock Joplin Investigation</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>https://www.kcur.org/news/2026-06-29/automated-license-plate-readers-alpr-kansas-city-lenexa-weston-police</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="3" t="inlineStr"/>
-      <c r="S33" s="3" t="inlineStr">
+      <c r="P33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>FLK-2026-011</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Monroe County Sheriff's Office</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Sheriff's Deputy Lamar Roman</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Flock Safety / ALPR</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Stalking / Unlawful Traffic Stop</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Deputy Roman allegedly used an ALPR system to track and eventually pull over a woman he had met while providing off-duty security on a television set, monitoring her private vehicular movements.</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Victim complaint and internal affairs investigation</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Arrested in 2026 and charged with accessing a computer or electronic device without authorization.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Monroe County SO / Local 10 / Law&amp;Crime (Mar 2026)</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>https://www.local10.com/news/local/2026/03/10/florida-keys-deputy-arrested-on-computer-crimes-charges/</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Local10 / Law&amp;Crime / 404 Media: Dep. Lamar Eliseo Roman fired+arrested Mar 2026; DAVID/ALPR hotlist + unauthorized stop of woman met on Bad Monkey set. Primary Monroe County case. Canonical Monroe County Lamar Roman record (FLK-2024-031 removed as duplicate of this case).</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="P34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>FLK-2026-012</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Prairie Grove &amp; Holiday Hills Police Dept.</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Officer / Chief William C. Copp</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Multiple (Unspecified)</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Officer Copp, who simultaneously served as Police Chief of nearby Holiday Hills, abused authorized police access to search Flock ALPR databases for vehicle locations of several former romantic partners and at least one of their new partners.</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Internal police investigation and victim reporting</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Arrested in 2026 and criminally charged with official misconduct and LPR misuse.</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Stalking Review</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>IJ Plate Privacy list: Officer/Chief William C. Copp Prairie Grove/Holiday Hills; arrested for Flock searches of former romantic partners.</t>
         </is>
       </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="P35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>FLK-2026-013</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>San Francisco PD &amp; Los Altos PD</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Municipal Operators &amp; Federal Agencies</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Mass Surveillance / Illegal Data Sharing</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>2,600,000+ (Systemic)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>A class action lawsuit revealed that federal immigration and law enforcement agencies accessed SFPD's Flock cameras over 1.6 million times, while Los Altos shared data over 1 million times with out-of-state agencies, violating California statutory privacy laws designed to protect civil liberties and immigrant communities.</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Public records disclosures and class action legal investigation</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Class action lawsuit filed by Gibbs Mura against Flock Safety and municipal operators seeking statutory damages ($2,500/violation) and injunctions.</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Gibbs Mura Class Action Complaint / California Civil Code § 1798.90.54 (April 2026)</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>https://www.classlawgroup.com/flock-safety-license-plate-reader-cameras-lawsuit</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="P36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>FLK-2026-014</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>San Diego Police Department</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Detective Gary Gonzales / Patrol Officers</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / False Arrest</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>San Diego police relied on a false Flock hit to arrest Ariel Beltran and Parra at gunpoint inside a cigar lounge for an attempted carjacking 5 miles away. The camera hit occurred before the pursuit began, proving physical impossibility, yet police ignored cell phone location alibis and arrested both men.</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Defense investigation proving physical alibi and impossible timestamp synchronization</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Criminal charges dismissed; victims filed formal civil rights tort claims seeking $1.5 million apiece in damages in April 2026.</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Times of San Diego Legal Investigation (June 2026)</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>https://timesofsandiego.com/crime/2026/06/07/a-flock-license-plate-reader-linked-a-san-diego-man-to-a-violent-crime-he-was-five-miles-away/</t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Times of San Diego Jun 2026: Hugo Parra AI vehicle match false positive; jailed ~1 month; charges dropped.</t>
         </is>
       </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr">
+      <c r="P37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>FLK-2026-015</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="B38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>MN</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Plymouth Police Department</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / False Stop</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Multi-day Flock tracking; high-risk box-and-pin stop June 28, 2026</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Automotive journalist Joel Feder and his wife were boxed in by four Plymouth PD squad cars outside a Kohl's after Flock ALPR alerts on a Range Rover press loaner. Police had tracked the vehicle for days via Flock. Root cause: a lost NJ manufacturer plate reported in California was entered into NCIC incomplete as 34 DTM (missing small middle digits); Feder's plate was 34 10 DTM, and Flock OCR also missed those characters. VIN clean; original plate was lost, not stolen; ~1 hour detention.</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Roadside verification (VIN/plate); Plymouth PD statement; Feder first-person account; local TV body-cam reporting</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Released at scene without charges; Plymouth PD attributed alerts to incomplete NCIC entry; Flock stated it was reviewing the incident.</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>The Drive (Feder) / FOX 9 Minneapolis / CBS Minnesota</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>https://www.thedrive.com/news/how-flock-cameras-wrongly-tracked-me-for-days-over-stolen-plates-and-sent-police-after-me</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Primary: Feder The Drive first-person. Local TV: FOX 9 (https://www.fox9.com/news/minnesota-car-reviewer-flock-camera) and CBS Minnesota/WCCO (https://www.cbsnews.com/minnesota/news/flock-cameras-wrongly-flag-plates-as-stolen/). Cross-listed as AI Wrongful Enforcement Database ID 42.</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="P38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>Incident late June 2026 (NCIC entry June 24; Flock alerts June 26 and June 28 stop).</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>Released / No Charges: Documented False Stop</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>FLK-2026-016</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Cherry Hills Village Police Dept.</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Wrongful Stop</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Flock Safety camera data led police to conduct an improper traffic stop on an innocent driver due to character misinterpretation and database synchronization errors.</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Roadside investigation and license plate verification</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Driver released without charges; documented in national civil rights review of ALPR accuracy failures.</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr">
+      <c r="P39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>FLK-2026-017</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="B40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Sherwood Police Department</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Patrol Officers / Automated System</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Flawed AI Recognition / Gunpoint Detention</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>1 (AI Error)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>A Flock camera misread the license plate of an SUV, leading officers to detain an innocent couple at gunpoint while their six-week-old baby sat alone in a car seat in the back of the vehicle.</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Roadside verification after armed detention</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Officers admitted the AI camera error on scene ('I'm not gonna say they're completely perfect...'); documented in national civil rights review.</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Institute for Justice ALPR Error Report</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>https://ij.org/dozens-of-innocent-motorists-have-been-pulled-over-detained-at-gunpoint-or-jailed-due-to-ai-license-plate-camera-errors/</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Cited / aggregator-aligned</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Retained from master workbook; cited source URL present and cross-checked against IJ/AJC/KCUR/EFF aggregator reporting where applicable.</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr">
+      <c r="P40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
         <is>
           <t>Civil Lawsuit / Settlement / Dismissed Stop</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>FLK-2026-018</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Baytown Police Department</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Unnamed officer (not publicly identified)</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Allegations under investigation (count not public)</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>In late July 2026, Baytown Police Chief John Stringer announced allegations that one officer misused the city’s Flock Safety license plate reader system. Stringer authorized an internal affairs investigation and a separate criminal investigation, and asked the Harris County District Attorney’s Office to assist. Chron reported August 2, 2026 that the officer resigned amid the open investigation. The officer has not been publicly named; allegations, not a finding of guilt.</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Agency receipt of allegations; chief public announcement; DA referral</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Officer resigned amid open internal and criminal investigations (reported Aug. 2, 2026); Harris County DA assisting; no public disposition naming the officer.</t>
         </is>
       </c>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>KPRC 2 / Click2Houston; ABC13; Houston Chronicle; Chron (Aug. 2, 2026)</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>https://www.click2houston.com/news/local/2026/07/27/baytown-police-investigating-officer-accused-of-misusing-flock-license-plate-reader-system/</t>
         </is>
       </c>
-      <c r="N41" s="3" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Chief Stringer public statement and DA referral confirmed in KPRC 2 / ABC13 / Chronicle; Chron Aug 2 Houston-area cluster notes resignation. Officer unnamed.</t>
         </is>
       </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr">
+      <c r="P41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>Announced late July 2026; resignation reported Aug. 2, 2026; probes ongoing.</t>
         </is>
       </c>
-      <c r="S41" s="3" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>FLK-2026-019</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Greer Police Department</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Kareem Lynch; Sebastian Echeverry</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Repeated unauthorized searches (per separation documents summarized in reporting)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Greer Police terminated Kareem Lynch (June 26, 2026) and Sebastian Echeverry (June 29, 2026) after an internal investigation alleged unauthorized Flock searches. Reporting on separation documents says Lynch searched plates of an officer he had previously been in a relationship with and entered inaccurate reasons; Echeverry allegedly searched multiple plates and falsely entered “Alcohol Offense Non-DUI.” Department said no criminal charges. Allegations from IA, not court findings.</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Internal investigation; separation documents described in Greenville Online reporting</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Both officers terminated (June 2026); no criminal charges announced per department.</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Greenville Online (July 24, 2026)</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>https://www.greenvilleonline.com/story/news/crime/2026/07/24/greer-pd-flock-scandal-upstate-police-oversight/90994284007/</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Greenville Online Jul 24 2026 names Lynch and Echeverry terminations and alleged false search reasons.</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="P42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>Terminations late June 2026; public reporting July 24.</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>FLK-2026-020</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Sumter County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Detective Brandy Almany</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Multiple restricted-database lookups alleged (Flock + DAVID + CCIS)</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Sumter County Sheriff’s Office announced an internal audit flagged Det. Brandy Almany’s use of restricted databases. Agency alleges she used Flock ALPR, Florida’s DAVID, and CCIS to obtain information about her husband’s ex-wife for personal reasons, and used unrelated case numbers / false electronic records to make searches appear investigative. Arrested on official misconduct and computer-related charges and terminated. Sheriff Patrick Breeden ordered a complete internal audit and suspended the agency’s use of Flock pending review. Allegations, not a finding of guilt.</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Internal audit of restricted databases; sheriff public statement</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Arrested and terminated (July 2026); agency suspended Flock use during audit; charges pending.</t>
         </is>
       </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>WESH 2; WFTV 9; ClickOrlando / News 6</t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>https://www.wesh.com/article/sumter-detective-arrested-database-misuse/73251430</t>
         </is>
       </c>
-      <c r="N43" s="3" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>WESH/WFTV/ClickOrlando Jul 23 to 24 2026: arrest, termination, Flock suspension. Allegations pending.</t>
         </is>
       </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr">
+      <c r="P43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>Arrest/termination/Flock suspension announced ~July 23 to 24, 2026.</t>
         </is>
       </c>
-      <c r="S43" s="3" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>FLK-2026-021</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="B44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Fayetteville Police Department</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Three unnamed officers</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Own plates and/or family/acquaintance plates (per agency release)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>During activation/testing of a new internal auditing feature, Fayetteville PD identified license-plate searches inconsistent with authorized use. The department said three employees searched their own plates or those of a family member/acquaintance without a legitimate law-enforcement purpose. All three were placed on administrative leave and later terminated. FPD requested GBI criminal investigation; names not disclosed; no charges announced at termination reporting.</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>New internal auditing feature activation/testing</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Three officers terminated (July 2026); GBI criminal investigation requested; charges not announced in initial reporting.</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Fayetteville PD statement / Atlanta News First / AJC / The Citizen</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>https://www.atlantanewsfirst.com/2026/07/17/3-fayetteville-police-officers-fired-accused-misusing-flock-camera-system/</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Agency news release and ANF/AJC/Citizen Jul 17 to 18 2026 coverage. Officers unnamed.</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="P44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>Firings announced ~July 17, 2026.</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>FLK-2026-022</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Henry County Police Department</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Patrick Isbell</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Accessed retained license plate data for non-law-enforcement purposes (per agency)</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Henry County Police fired and arrested officer Patrick Isbell, 41, charged with misuse of license plate data on July 10, 2026 after an internal audit found he accessed the department’s Flock network and used retained plate data for non-law-enforcement purposes. Investigation ongoing. Allegations/charges, not a conviction.</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Internal audit</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Fired and arrested; charged with misuse of license plate data (July 10, 2026); investigation ongoing.</t>
         </is>
       </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>AJC (July 2026 Georgia wave coverage)</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>https://www.ajc.com/news/2026/07/3-more-georgia-police-officers-fired-over-alleged-flock-camera-misuse/</t>
         </is>
       </c>
-      <c r="N45" s="3" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>AJC names Isbell, July 10 charge, Henry County internal audit finding.</t>
         </is>
       </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="inlineStr">
+      <c r="P45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>Charge date July 10, 2026 per AJC.</t>
         </is>
       </c>
-      <c r="S45" s="3" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>FLK-2026-023</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="B46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>DeKalb County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Sgt. Kabiru Salawu</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Unauthorized Flock use (specific search details not released in initial reporting)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>DeKalb County Sheriff’s Office fired and arrested Sgt. Kabiru Salawu, a ~17-year veteran, after an internal probe identified alleged misuse of Flock license plate reader technology. Charged with misuse of license plate data and felony violation of oath of office. Specific search targets not detailed in initial agency/press coverage. Allegations/charges, not a conviction.</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Internal probe</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Terminated and arrested (July 2026); charged with misuse of license plate data and violation of oath.</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>DeKalb County SO announcement / USA Today / AJC / Reason</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>https://www.usatoday.com/story/news/state/georgia/atlanta/2026/07/21/veteran-atlanta-deputy-adds-to-growing-list-of-ga-cops-misusing-flock/90992565007/</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>USA Today / AJC / Reason late July 2026 name Salawu and charges.</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="P46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>Arrest/firing reported ~July 18 to 21, 2026.</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>FLK-2026-024</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="B47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Conyers Police Department (Real-Time Crime Center)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Paige Forte (dispatcher / RTCC supervisor)</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>More than 30 Flock accesses April to July 2026 (GBI preliminary)</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>After an internal Flock audit, Conyers PD requested a GBI investigation of RTCC supervisor Paige Forte. Preliminary information indicates she accessed Flock more than 30 times between April and July 2026 for non-law-enforcement purposes; department said inquiries involved her domestic partner’s vehicle to ascertain location. GBI arrested Forte July 22, 2026 and charged Misuse of a License Plate Reader System. Placed on administrative leave pending internal review. Allegations/charges, not a conviction.</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Internal Flock audit; GBI investigation requested by Conyers PD</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Arrested July 22, 2026 (Misuse of a License Plate Reader System); administrative leave; GBI investigation ongoing for DA review.</t>
         </is>
       </c>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>GBI press release (July 23, 2026); Conyers PD / WSB / FOX 5</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>https://gbi.georgia.gov/press-releases/2026-07-23/gbi-arrests-conyers-police-department-employee-misuse-license-plate</t>
         </is>
       </c>
-      <c r="N47" s="3" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>GBI Jul 23 2026 press release: Forte arrest, &gt;30 accesses Apr to Jul 2026. Partner-tracking detail in Conyers PD / WSB coverage.</t>
         </is>
       </c>
-      <c r="P47" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q47" s="3" t="inlineStr"/>
-      <c r="R47" s="3" t="inlineStr">
+      <c r="P47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>Arrest July 22, 2026; GBI release July 23.</t>
         </is>
       </c>
-      <c r="S47" s="3" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>FLK-2026-025</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="B48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Fort Bend County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Unnamed lieutenant</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>About 148 searches of one plate; about 41 of another (2022–2025)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Internal-affairs documents obtained by ABC13 and summarized by Chron show a Fort Bend County Sheriff’s Office lieutenant searched one woman’s license plate about 148 times and another plate about 41 times from 2022 through 2025. The lieutenant admitted the searches were not for official sheriff’s-office purposes. The woman reported fearing stalking after checking Have I Been Flocked. Reporting says the agency found a general-orders violation and imposed a two-day suspension.</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Victim complaint after Have I Been Flocked lookup; internal affairs docs</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Found to have violated general orders; two-day suspension reported (ABC13 / Chron). No criminal conviction catalogued here.</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>ABC13; Chron (Aug. 2, 2026 Houston-area cluster)</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>https://abc13.com/post/fort-bend-county-sheriffs-office-lieutenant-admits-improper-use-flock-cameras-docs/19528986/</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>ABC13 IA document reporting; Chron Aug 2 cluster corroboration.</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>2022-2025</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="Q48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>Search window 2022–2025; discipline reported mid-2026 / Chron Aug 2.</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>Internal Disciplinary Action / Other</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>FLK-2026-026</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="B49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Savannah Police Department</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Four officers and two civilian employees (unnamed)</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Multiple flagged searches (counts not fully public)</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Savannah Police announced that an internal audit under Flock’s Audit Assistance Program flagged potential misuse by four officers and two civilian employees. All six were placed on administrative leave; discipline up to termination is on the table; cases referred to the Georgia Bureau of Investigation. Alleged searches included personal acquaintances and family members; one officer allegedly shared SPD Flock access with personnel from an outside agency. Internal investigation began July 27, 2026.</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Flock Audit Assistance / agency Office of Professional Standards audit</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Six employees on administrative leave; GBI criminal referral; possible termination; investigations ongoing as of early August 2026 reporting.</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>WJCL; WTOC; WRDW</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>https://www.wjcl.com/article/savannah-police-flock-system-misuse-investigation/73321620</t>
         </is>
       </c>
-      <c r="N49" s="3" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>SPD / mayor statements carried by WJCL (July 31) and WRDW (Aug 2).</t>
         </is>
       </c>
-      <c r="P49" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr"/>
-      <c r="R49" s="3" t="inlineStr">
+      <c r="P49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>Leave / GBI referral announced July 31, 2026; disposition pending.</t>
         </is>
       </c>
-      <c r="S49" s="3" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>Under Investigation / Pending</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>FLK-2026-027</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="B50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Charlotte-Mecklenburg Police Department</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Officer Seth Daniel Elliott</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>At least one alleged plate query for a friend (drug target)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>On July 29, 2026, CMPD Officer Seth Daniel Elliott was arrested and charged with illegally accessing a government computer. An SBI affidavit summarized in local reporting says a friend who was the target of a Watauga County drug investigation asked Elliott to run a plate; investigators allege Elliott queried Flock Safety and CJLEADS, learned it belonged to an undercover officer’s vehicle, and relayed that over Snapchat. CMPD placed Elliott on unpaid leave and revoked database access. On August 4, CMPD released its Flock MOU under press pressure: CMPD does not own Flock cameras but gets network access (including limited community devices) via the MOU; the trial period was extended past May.</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>SBI investigation / charging affidavit; local investigative reporting</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Arrested and charged (illegal access to a government computer); unpaid administrative leave; database access revoked. Allegations / charges, not a conviction.</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>WBTV; Spectrum News; WSOC</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>https://www.wbtv.com/2026/07/30/arrested-charlotte-mecklenburg-police-officer-accused-giving-information-investigation-target/</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>WBTV July 30 arrest story; WBTV Aug 4 MOU release. Charging allegations pending.</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="P50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>Arrest July 29, 2026; MOU released Aug 4, 2026.</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>FLK-2026-028</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>OH</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Reynoldsburg Police Department</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Two unnamed officers</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>One officer: 50+ non-work searches over ~6 months (records)</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>NBC4 reported August 4, 2026 that two Reynoldsburg Police officers resigned within about two months amid internal reviews of possible Flock misuse. Records described for one officer show more than 50 non-work-related searches over six months; that officer resigned effective July 16, the day before a scheduled administrative review. Chief Curtis Baker said non-law-enforcement use of Flock or other police databases will not be tolerated. Criminal charges were unclear in that reporting.</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Internal investigation; chief news release after NBC4 inquiry</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Both officers resigned; possible criminal charges unclear as of Aug. 4, 2026 reporting.</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>NBC4 WCMH-TV (Aug. 4, 2026)</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>https://www.nbc4i.com/news/local-news/reynoldsburg/reynoldsburg-officer-may-have-misused-flock-cameras-records-show/</t>
         </is>
       </c>
-      <c r="N51" s="3" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>NBC4 Aug 4 reporting quoting Chief Baker release and internal records description.</t>
         </is>
       </c>
-      <c r="P51" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q51" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R51" s="3" t="inlineStr">
+      <c r="P51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>Resignations reported Aug. 4, 2026 (one effective July 16).</t>
         </is>
       </c>
-      <c r="S51" s="3" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>FLK-2026-029</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="B52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Habersham County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Deputy Christian Brewer</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Romantic Stalking</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Personal-relationship searches (counts not fully public)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Atlanta News First reported July 31, 2026 that Habersham County Deputy Christian Brewer was fired and arrested after allegedly using the department’s Flock license plate reader system for reasons unrelated to his job. The sheriff’s office said the searches involved someone he was in a personal relationship with. Charges reported: one count of felony violation of oath of office and two counts of misdemeanor misuse of license plate data. Allegations and charging documents as reported, not a conviction.</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Flock Audit Assistance / agency internal audit</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Fired and arrested; felony oath-of-office count plus misdemeanor plate-data misuse counts reported (ANF July 31, 2026).</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>Atlanta News First (July 31, 2026)</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>https://www.atlantanewsfirst.com/2026/07/31/habersham-county-deputy-fired-arrested-after-flock-license-plate-reader-audit/</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>ANF Investigates naming Brewer; sheriff Robin Krockum statement quoted.</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="P52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>Fired and arrested; reported July 31, 2026.</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>FLK-2026-030</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Coweta County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Three unnamed employees</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Accounts flagged in self-initiated audit (details not public)</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>On August 4, 2026, the Coweta County Sheriff’s Office said three employees resigned after a self-initiated Flock Safety audit flagged their accounts for additional review. Each resigned during meetings with department leaders before the audit finished and before an internal investigation opened. The agency asked the Georgia Bureau of Investigation to investigate independently and said it would add training for Flock users. Employees were not publicly identified; alleged misuse details were not released.</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Self-initiated agency Flock audit / Audit Assistance tooling</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Three employees resigned before internal investigation; GBI independent investigation requested (Aug. 4, 2026 reporting).</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Atlanta News First; FOX 5 Atlanta; WSB-TV</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>https://www.atlantanewsfirst.com/2026/08/04/3-coweta-county-sheriffs-office-employees-resign-after-flock-audit/</t>
         </is>
       </c>
-      <c r="N53" s="3" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Agency statement carried by ANF / FOX 5 / WSB; names and search details withheld.</t>
         </is>
       </c>
-      <c r="P53" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q53" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="R53" s="3" t="inlineStr">
+      <c r="P53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R53" t="inlineStr">
         <is>
           <t>Resignations and GBI referral announced Aug. 4, 2026.</t>
         </is>
       </c>
-      <c r="S53" s="3" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>FLK-2026-031</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="B54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Bibb County Sheriff’s Office</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Deputies under review (unnamed; three flagged queries)</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Flock Safety</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Unauthorized Access / Personal Tracking</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Three separate queries flagged by monthly audit algorithm</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>On August 3–4, 2026, the Bibb County Sheriff’s Office said its routine monthly Flock audit returned three separate queries flagged as problematic by Flock’s auditing algorithm. Internal Affairs is reviewing whether any deputies violated policy. Officials said no deputies had been terminated or placed on administrative leave, but those under review had Flock access suspended pending the outcome. The agency said it would publicly disclose confirmed findings of misuse when investigations finish. Allegations under investigation, not findings of guilt.</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Monthly agency Flock audit / Audit Assistance algorithm</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Internal Affairs investigations open; Flock access suspended for deputies under review; no firings or leave announced as of Aug. 3–4 reporting.</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Georgia Public Broadcasting; WGXA; Macon Telegraph; 41NBC</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>https://www.gpb.org/news/2026/08/04/bibb-county-sheriffs-office-launches-investigation-for-potential-misuse-of-flock</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Agency statement carried by GPB / WGXA / Macon Telegraph / 41NBC; names and query details withheld; investigations active.</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="P54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>Investigations announced Aug. 3–4, 2026; outcomes pending.</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>Under Investigation / Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FLK-2026-032</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mooresville Police Department</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Officer Elizabeth Anne Snowman</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Romantic Stalking</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>31 alleged Flock searches (chief stated; some off-duty)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Mooresville Police Chief Ron Campurciani said a Flock audit found Officer Elizabeth Anne Snowman accessed the LPR system 31 times to track her boyfriend’s ex-wife, including at least two off-duty accesses. Most searches allegedly listed motor-vehicle infractions as the reason. Snowman, 36, was arrested Aug. 5, 2026, and charged with misdemeanor accessing computers (N.C.G.S. 14-454). The chief said the department will require case numbers on future Flock searches and that other officers were under review. Employment status was mixed in early reporting (still employed pending HR vs. some accounts calling her former). Allegations and charging documents as reported, not a finding of guilt.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Internal monthly Flock audit; chief press conference; arrest warrant</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Arrested and charged Aug. 5, 2026 (misdemeanor accessing computers); $5,000 bond; court appearance set Aug. 27 in early reporting; employment disposition pending / mixed in same-day coverage.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>ABC News; WSOC; Spectrum News; WCCB Charlotte</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://abcnews.com/US/officer-allegedly-flock-license-plate-cameras-track-boyfriends/story?id=135418955</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Chief Campurciani public statements and warrant coverage Aug. 5–6, 2026 across ABC / WSOC / Spectrum / WCCB. Same misdemeanor computer-access charge family as CMPD Elliott.</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Arrest/charge announced Aug. 5, 2026; disposition pending.</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Criminally Charged / Indicted</t>
         </is>
       </c>
     </row>

--- a/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
+++ b/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Former Officer Coty Hall</t>
+          <t>Former Officer Coty Wayne Hall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1501,32 +1501,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Multiple (Unspecified)</t>
+          <t>About 192 alleged Flock searches</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Officer Hall utilized the department's Flock camera network to unlawfully track the personal driving routes and movements of a fellow police officer and that officer's spouse.</t>
+          <t>Niceville Officer Coty Wayne Hall was arrested Oct. 10, 2025 after an internal audit (Jan.–Oct. 2025) found unauthorized database and Flock ALPR searches used to track and harass a fellow officer and that officer’s spouse. Reporting cites about 192 inappropriate Flock searches and access to other restricted systems. The city fired Hall. Under an April 20, 2026 plea recommendation he pleaded no contest to amended computer-access and related charges; the court withheld adjudication and imposed about 11 months of probation, community service, and a permanent no-contact order (Mid Bay News).</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Internal department audit and complaint</t>
+          <t>Internal department audit after concerns about database misuse</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Pleaded no contest to criminal charges; fired from the police department following arrest.</t>
+          <t>Fired after Oct. 2025 arrest; April 2026 no-contest plea; probation / withheld adjudication reported.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Institute for Justice / Florida Court Records</t>
+          <t>Mid Bay News; R News / affidavit reporting; Washington Post / DNYUZ roundup</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://ij.org/police-have-reportedly-used-license-plate-readers-to-stalk/</t>
+          <t>https://midbaynews.com/post/former-niceville-cop-no-contest-in-flock-stalking-case</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1536,18 +1536,20 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>IJ: Niceville Officer Coty Hall; Flock tracking of coworker+spouse; pleaded no contest; fired (arrest ~Oct 2025).</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>2024</v>
+          <t>Arrest Oct 2025; Mid Bay plea writeup cites April 20, 2026 sentence recommendation; ~192 searches in WaPo-syndicated roundup.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="Q13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Misuse discovery/ID year 2024; arrest ~Oct 2025 then plea / termination.</t>
+          <t>Misuse window 2025; Case_ID year 2024 catalog vintage; plea April 2026.</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1745,7 +1747,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Former Deputy Chris Rozar</t>
+          <t>Former Deputy Chris Ashley Rozar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1760,32 +1762,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Multiple (Unspecified)</t>
+          <t>Multiple Flock / tag-reader / GCIC lookups alleged (counts not fully public)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Deputy Rozar utilized the department's Flock Safety ALPR database to monitor the movements of a woman he was romantically interested in, tracking her vehicle locations without her consent or any active criminal case.</t>
+          <t>Coffee County Deputy Chris Ashley Rozar was terminated when a GBI investigation began after a woman alleged stalking (~2024). Court records summarized by WALB say he improperly used the sheriff’s Flock camera and tag-reader system plus GCIC for personal tracking (incidents alleged around April–May 2024). On May 5, 2026, after a Coffee County grand jury indictment, he was arrested on eight counts including violation of oath, computer invasion of privacy, prohibited use of captured license plate data, and stalking.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Victim complaint and subsequent internal investigation</t>
+          <t>Victim complaint; former sheriff requested independent GBI investigation</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Fired from the department at the onset of the investigation; criminally charged with multiple offenses.</t>
+          <t>Fired at investigation onset (~2024); arrested May 5, 2026 on multi-count indictment; case pending.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution / Institute for Justice</t>
+          <t>Coffee County Sheriff’s Office press; WALB; Douglas Now</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.ajc.com/news/2026/06/georgia-officers-misuse-license-plate-reader-databases-can-they-be-stopped/</t>
+          <t>https://www.coffeesheriffga.gov/press/chris-ahsley-rozar</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1795,13 +1797,19 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>IJ/AJC: Coffee County former Dep. Chris Rozar charged after Flock stalking of romantic interest; fired.</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>2025</v>
-      </c>
-      <c r="R16" t="inlineStr"/>
+          <t>Agency press + WALB May 5–8 2026 detail Flock/tag-reader misuse and indictment.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Misuse alleged 2024; Case_ID 2025; arrest/indictment May 2026.</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
@@ -5120,7 +5128,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Officer Elizabeth Anne Snowman</t>
+          <t>Former Officer Elizabeth Anne Snowman (plus ~10 other officers under review)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5140,7 +5148,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mooresville Police Chief Ron Campurciani said a Flock audit found Officer Elizabeth Anne Snowman accessed the LPR system 31 times to track her boyfriend’s ex-wife, including at least two off-duty accesses. Most searches allegedly listed motor-vehicle infractions as the reason. Snowman, 36, was arrested Aug. 5, 2026, and charged with misdemeanor accessing computers (N.C.G.S. 14-454). The chief said the department will require case numbers on future Flock searches and that other officers were under review. Employment status was mixed in early reporting (still employed pending HR vs. some accounts calling her former). Allegations and charging documents as reported, not a finding of guilt.</t>
+          <t>Mooresville Police Chief Ron Campurciani said a Flock audit found Officer Elizabeth Anne Snowman accessed the LPR system 31 times to track her boyfriend’s ex-wife, including at least two off-duty accesses. Most searches allegedly listed motor-vehicle infractions as the reason. Snowman, 36, was arrested Aug. 5, 2026, and charged with misdemeanor accessing computers. The chief said the audit flagged about 11 officers’ activity and that roughly 10 other cases were under review (about three described as more serious), with possible additional charges. Same-week reporting described Snowman as no longer with MPD. Department will require case numbers on future Flock searches. Allegations pending for others.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5150,12 +5158,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Arrested and charged Aug. 5, 2026 (misdemeanor accessing computers); $5,000 bond; court appearance set Aug. 27 in early reporting; employment disposition pending / mixed in same-day coverage.</t>
+          <t>Arrested and charged Aug. 5, 2026; reporting describes her as former MPD; ~10 additional officers under review; case-number rule announced.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ABC News; WSOC; Spectrum News; WCCB Charlotte</t>
+          <t>ABC News; WSOC; Spectrum News; WCCB; WHKY; WFAE</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5170,20 +5178,23 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Chief Campurciani public statements and warrant coverage Aug. 5–6, 2026 across ABC / WSOC / Spectrum / WCCB. Same misdemeanor computer-access charge family as CMPD Elliott.</t>
+          <t>Chief statements Aug 5–6 2026; WHKY notes 11 officers flagged; WSOC says no longer with MPD.</t>
         </is>
       </c>
       <c r="P55" t="n">
         <v>2026</v>
       </c>
+      <c r="Q55" t="n">
+        <v>2026</v>
+      </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Arrest/charge announced Aug. 5, 2026; disposition pending.</t>
+          <t>Arrest Aug. 5, 2026; employment fallout reported same week; probe of others ongoing.</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Criminally Charged / Indicted</t>
+          <t>Terminated / Resigned &amp; Criminally Charged</t>
         </is>
       </c>
     </row>

--- a/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
+++ b/docs/Flock_Safety_ALPR_Misuse_Master_Database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Savannah Police announced that an internal audit under Flock’s Audit Assistance Program flagged potential misuse by four officers and two civilian employees. All six were placed on administrative leave; discipline up to termination is on the table; cases referred to the Georgia Bureau of Investigation. Alleged searches included personal acquaintances and family members; one officer allegedly shared SPD Flock access with personnel from an outside agency. Internal investigation began July 27, 2026.</t>
+          <t>Savannah Police announced that an internal audit under Flock’s Audit Assistance Program flagged potential misuse by four officers and two civilian employees. All six were placed on administrative leave July 31, 2026, and cases were referred to the Georgia Bureau of Investigation. Alleged searches included personal acquaintances and family members; one officer allegedly shared SPD Flock access with personnel from an outside agency. On August 7, 2026, SPD announced all six employees had been terminated after the administrative investigation found policy violations. GBI’s criminal investigation remains ongoing; names withheld pending that probe and appeals.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4621,17 +4621,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Six employees on administrative leave; GBI criminal referral; possible termination; investigations ongoing as of early August 2026 reporting.</t>
+          <t>All six employees terminated Aug. 7, 2026 (SPD release); GBI criminal investigation ongoing; names not released.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>WJCL; WTOC; WRDW</t>
+          <t>Savannah PD release; WTOC; Savannah Morning News; WJCL; WRDW</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.wjcl.com/article/savannah-police-flock-system-misuse-investigation/73321620</t>
+          <t>https://savannahpd.org/savannah-police-department-terminates-six-employees-following-investigation-into-misuse-of-flock-safety-system/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4641,20 +4641,23 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>SPD / mayor statements carried by WJCL (July 31) and WRDW (Aug 2).</t>
+          <t>SPD Aug. 7 termination release; WTOC / Savannah Morning News same-day coverage; earlier leave/GBI referral July 31.</t>
         </is>
       </c>
       <c r="P49" t="n">
         <v>2026</v>
       </c>
+      <c r="Q49" t="n">
+        <v>2026</v>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Leave / GBI referral announced July 31, 2026; disposition pending.</t>
+          <t>Leave / GBI referral July 31, 2026; administrative terminations Aug. 7, 2026; criminal probe pending.</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Under Investigation / Pending</t>
+          <t>Terminated / Resigned (Employment Fallout)</t>
         </is>
       </c>
     </row>
@@ -5195,6 +5198,187 @@
       <c r="S55" t="inlineStr">
         <is>
           <t>Terminated / Resigned &amp; Criminally Charged</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FLK-2026-033</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Polk County Police Department / Cedartown Police Department Flock access (Northwest Georgia Drug Task Force)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Former Officer Tracey Royston (Cedartown / Polk County)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Unauthorized Access / Personal Tracking</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Multiple alleged non-LE accesses 2024–2025 (counts not fully public)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>The Georgia Bureau of Investigation arrested former Polk County Police Officer Tracey Royston, 51, of Cedartown, on August 7, 2026, on four misdemeanor counts of misuse of a license plate reader system. At the time of the alleged crimes she served on the Northwest Georgia Drug Task Force (managed by the GBI) and had access to Cedartown Police Department’s Flock Safety system. Cedartown police asked the GBI to investigate on July 31, 2026. GBI’s preliminary investigation indicates Royston accessed the Flock system multiple times between 2024 and 2025 for non-law-enforcement purposes. She was booked into Polk County Jail. Allegations and charging documents as reported, not a finding of guilt by this catalog.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Cedartown PD referral to GBI (July 31, 2026); GBI arrest Aug. 7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Arrested Aug. 7, 2026 on four misdemeanor LPR-misuse counts; described as former Polk County officer; case pending.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Atlanta News First / GBI</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://www.atlantanewsfirst.com/2026/08/07/gbi-arrests-former-polk-county-police-officer-allegedly-misusing-flock-camera-system/</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>ANF Aug. 7, 2026 citing GBI; Cedartown Flock access via task-force assignment.</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Alleged accesses 2024–2025; GBI arrest Aug. 7, 2026.</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Criminally Charged / Indicted</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FLK-2026-034</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Chandler Police Department</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Unnamed Chandler police employee (one person per mayor-elect)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Flock Safety</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Unauthorized Access / Personal Tracking</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Routine audit anomaly found Aug. 6, 2026 (details not public)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Chandler Police Chief Bryan Chapman said a routine audit of Flock data found an unexplained “anomaly in the use of the Flock system that could not be explained through standard police action” on August 6, 2026. On August 7 the city announced it was ending its about $153,000 Flock contract (about 40 cameras). Chapman said an internal investigation would determine whether Flock was used inappropriately and that discipline would follow if so; he declined specifics. Mayor-elect Matt Orlando said to his knowledge only one employee was involved. City statement said no resident’s privacy had been compromised. Allegations under investigation, not a finding of guilt.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Routine 30-day / quarterly / annual Flock audit (chief statement)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Internal investigation open as of Aug. 7, 2026; contract terminated same day; discipline TBD if misuse confirmed.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>AZCentral / Arizona Republic (Aug. 7, 2026)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://www.azcentral.com/story/news/local/chandler-breaking/2026/08/07/chandler-arizona-discontinues-flock-cameras/91218403007/</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Chief Chapman / city release via AZCentral Aug. 7; employee unnamed; probe ongoing.</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Anomaly found Aug. 6, 2026; contract end announced Aug. 7; IA pending.</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Under Investigation / Pending</t>
         </is>
       </c>
     </row>
